--- a/Data/sat_items.xlsx
+++ b/Data/sat_items.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,76 +426,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>question_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>difficulty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source_text</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>editable_portion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>option_a</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>option_b</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>option_c</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>option_d</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>correct_answer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
@@ -492,7 +504,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e3494f3d-170d-4add-aa63-5f68783bb58e</t>
+          <t>5d930aa7-42ba-4fa0-9ea0-8261c83a3b6f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -512,34 +524,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The ancient city of Pompeii was once a vibrant center of Roman life, bustling with activity and commerce. However, the eruption of Mount Vesuvius in 79 CE abruptly transformed this lively metropolis into a silent archaeological site. Today, the preserved ruins offer a glimpse into daily routines that were suddenly interrupted, providing historians with invaluable, or extremely valuable, information about the past.</t>
+          <t>In early maps, coastlines were often drawn by guesswork rather than measurement. Later cartographers improved their methods by using fixed reference points—such as lighthouses—and by recording distances carefully. As a result, the new maps were not merely “different”; they were more accurate, with fewer confusing bends and missing bays. Even so, some errors remained because storms could shift the shoreline and because explorers sometimes reported their observations after returning inland. Thus, a map’s details may reflect both careful technique and the limits of the moment when it was made.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>In the passage, what does the word 'invaluable' most nearly mean?</t>
+          <t>In the passage, what does “recording” most nearly mean?</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>extremely precious</t>
+          <t>writing down</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>not valuable</t>
+          <t>guessing</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>measuring without notes</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>replaceable</t>
+          <t>erasing later</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,14 +561,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The word 'invaluable' is clarified by the phrase 'extremely valuable' in the passage, indicating that the correct meaning is 'extremely precious'.</t>
+          <t>The passage says cartographers “record distances carefully,” which indicates they document them—i.e., write them down—rather than guess, measure without documentation, or erase.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>c13acee7-0f7e-4423-ba56-f24509bdc17c</t>
+          <t>1fced7e0-f3e8-41f4-8547-446f6a8c7f38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -576,34 +588,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Although many regarded the invention as merely novel, its creator insisted it was transformative. This distinction was critical to her argument: a novel device might attract temporary attention, but a transformative one fundamentally alters existing practices. Her peers, however, remained skeptical, describing the innovation as intriguing yet lacking in substantial impact. Nonetheless, the inventor maintained that, over time, the device’s influence would become unmistakably significant.</t>
+          <t>In early astronomical records, observers described comets as “wandering” lights, a metaphor that suggested motion without explaining it. Later, when telescopes improved, the same objects were reclassified using more precise language: rather than wandering, they followed predictable orbits. This shift mattered because it changed what counts as evidence. A metaphor can guide attention, but it can also obscure mechanism. By replacing figurative terms with measurements—period, eccentricity, and brightness variation—astronomers made claims that could be tested and revised. In this way, vocabulary did not merely decorate discovery; it constrained interpretation, separating what was seen from what was inferred.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>In the passage, what does the word 'novel' most nearly mean?</t>
+          <t>In the passage, what does the word "constrained" most nearly mean?</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>temporary</t>
+          <t>celebrated</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>significant</t>
+          <t>ignored</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>complex</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,14 +625,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The context indicates that 'novel' is contrasted with 'transformative,' suggesting that 'novel' refers to something new and original, as opposed to having a lasting impact or significance.</t>
+          <t>The passage says that replacing metaphors with measurements made it possible to distinguish what was seen from what was inferred. That means the vocabulary did not open interpretation up in general; it restricted how people could interpret the evidence. Therefore, "constrained" most nearly means "limited."</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a07f312d-751e-4d03-9467-c9566b2d991c</t>
+          <t>9e90f2fc-cc9b-4b25-b7e2-87f9bd0d5ead</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -640,51 +652,51 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>While the term 'ephemeral' often evokes images of fleeting beauty, such as a blossom that withers by dusk, its implications in scientific discourse are considerably more nuanced. In environmental studies, an 'ephemeral' waterway describes a stream that exists only briefly after precipitation, distinguished from perennial rivers by its transitory nature. Thus, whereas in poetry 'ephemeral' may suggest the poignancy of impermanence, in scientific contexts it denotes a precise, observable temporality—one that is measured and anticipated, rather than merely lamented.</t>
+          <t>In the study of coastal sediments, researchers often distinguish between material that is merely transported and material that is actually reworked. Transport describes motion without substantial alteration; reworking implies that grains have been repeatedly disturbed—abrading edges, mixing layers, and resetting chemical conditions. This distinction matters because a core’s lower strata may appear continuous, yet the processes that shaped them can be inferred only if the terminology matches the mechanism. For example, when a report states that sand was “redistributed” after a storm, the word suggests displacement without substantial alteration, but it does not, by itself, guarantee reworking. Only evidence of abrasion, stratigraphic inversion, or renewed mineral reactions can bridge that gap.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>In the passage, what does the word 'ephemeral' most nearly mean in the context of scientific discourse?</t>
+          <t>According to the passage, in the context of the storm report, the word “redistributed” most nearly means that the sand was—</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Short-lived but beautiful</t>
+          <t>displaced without substantial alteration</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Measured and anticipated temporality</t>
+          <t>chemically changed without being displaced</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Poignant impermanence</t>
+          <t>disturbed repeatedly enough to abrade and reset conditions</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Perennial and enduring</t>
+          <t>deposited in the exact same order as before the storm</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>In the context of scientific discourse, 'ephemeral' is used to describe something that is temporary but with an observable duration that is measured and anticipated, as explained in the passage.</t>
+          <t>The passage states that in this context, “redistributed” suggests displacement without substantial alteration. That matches option A. Option C describes reworking—repeated disturbance with abrasion and resetting conditions—which the passage says “redistributed” alone does not guarantee. Option B involves chemical change without displacement, which the passage does not connect to the meaning of “redistributed.” Option D describes an ordering claim that the passage does not make.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e4892e3d-7bfa-4736-b3c1-3da716e25ef7</t>
+          <t>4315f9a6-5454-489e-88fa-0add269d589e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,34 +716,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Many people believe that eating breakfast is essential for a healthy lifestyle. According to this view, breakfast provides energy for the day and helps people focus in school or at work. In addition, supporters claim that those who eat breakfast are less likely to overeat later. However, some recent studies suggest that skipping breakfast does not always lead to negative health effects. Instead, these studies argue that the importance of breakfast may depend on individual needs and habits. Therefore, while breakfast can be beneficial for some, it is not necessarily required for everyone.</t>
+          <t>In many museums, labels beside objects aim to explain what viewers are seeing. They often begin with a clear description—where an item was found, what it is made of, and when it was made—so that visitors can form a basic timeline. However, a label can do more than report facts. For example, when a curator uses a phrase like “this suggests,” the writing signals that the information is an interpretation rather than a direct observation. As a result, readers learn not only about the artifact, but also about how historians reason. In contrast, labels that avoid such signals may lead visitors to treat every detail as equally certain, even when evidence is limited.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>How does the passage structure the argument about the importance of breakfast?</t>
+          <t>Which choice best describes the passage’s organization?</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>By presenting a widely held belief and then introducing evidence that challenges it.</t>
+          <t>It describes how museum labels often provide basic factual details, then explains how interpretive wording (such as “this suggests”) affects readers, and finally contrasts that effect with what can happen when labels avoid such signals.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>By outlining a cause-and-effect relationship between breakfast and health.</t>
+          <t>It argues that museum labels fail to help visitors understand artifacts, then uses examples of interpretation and evidence to support that claim, and ends by concluding that all labels should avoid interpretive language.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>By listing the benefits of breakfast before summarizing the main idea.</t>
+          <t>It presents a viewpoint about museum labels, then gives several different examples of specific label techniques, and concludes that visitors cannot distinguish between certainty levels.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>By comparing two different opinions on breakfast without taking a stance.</t>
+          <t>It defines interpretation, then shifts to a detailed account of how historians determine facts for labels, and ends by claiming that timelines are unnecessary for visitors.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -741,14 +753,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>The passage starts with the common belief that breakfast is essential, then presents studies that challenge this view, showing a contrast in perspectives.</t>
+          <t>The passage first explains the common structure of museum labels (they often start with basic factual details that form a timeline). It then introduces how interpretive phrasing like “this suggests” signals interpretation, and it explains the resulting effect on readers. Finally, it uses a contrast (“In contrast”) to explain a different effect when labels avoid such signals, even if evidence is limited. Option A is the only choice that matches this progression from general description to interpretive-language example to contrast about avoiding interpretive signals.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e8e44a4f-8a68-4fd3-82c6-a06a2e1e2bd4</t>
+          <t>75185ab8-59eb-4d9a-be92-a220a307c824</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,34 +780,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Many historians assert that the printing press, invented in the fifteenth century, was the primary catalyst for the spread of new ideas during the Renaissance. They argue that the ability to mass-produce books allowed knowledge to reach a broader audience, thereby accelerating cultural and scientific advancements. However, others contend that the flourishing of trade routes and increased mobility among scholars were equally significant. These critics maintain that, even before the press, networks of merchants and intellectuals facilitated the exchange of information across regions. Thus, while the printing press undoubtedly played a vital role, it was not the sole driver of Renaissance innovation.</t>
+          <t>In historical studies of climate, researchers often treat weather records as straightforward evidence of long-term change. Temperature measurements, for example, are compiled into continuous series and then compared across decades. This approach assumes that the instruments and observers merely report an external reality. However, the meaning of “change” depends on how those records were produced. Station moves, changes in calibration, and differences in reporting practices can alter what counts as a trend. Consequently, scholars increasingly pair statistical reconstructions with documentary analysis of field methods. In this way, the data do not simply reveal history; they also reflect the choices made while collecting it.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>How does the passage develop the argument about the role of the printing press in the Renaissance?</t>
+          <t>Which choice best describes the passage’s overall structure?</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>By contrasting the impact of the printing press with other factors that contributed to the spread of ideas.</t>
+          <t>It presents an initial claim about how climate researchers use weather records, then challenges that claim by explaining limitations, and concludes by describing an alternative approach.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>By listing the chronological events that led to the invention of the printing press.</t>
+          <t>It argues that documentary analysis is unnecessary, then provides a historical example to support that claim, and ends by refuting counterarguments.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>By focusing solely on the negative aspects of the printing press's influence.</t>
+          <t>It defines key terms related to climate study, then offers several unrelated reasons why temperature records can be misleading, and finishes with a brief summary.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>By presenting statistical data to demonstrate the printing press's effectiveness.</t>
+          <t>It compares two competing theories of climate change, then lists evidence for each theory, and concludes by endorsing one of them as definitive.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -805,14 +817,14 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>The passage develops the argument by contrasting the role of the printing press with other factors such as trade routes and scholar mobility, indicating that while the press was important, it was not the only driver of Renaissance innovation.</t>
+          <t>The passage begins by describing a common method (using weather records as straightforward evidence), then shifts to a critique (the meaning of “change” depends on production choices), and ends by proposing a combined method (statistical reconstructions paired with documentary analysis).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61b88777-6262-47e3-a6a6-829641a3580c</t>
+          <t>15b37d32-b49d-4afa-a75f-b90fa1fb81d0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -832,34 +844,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>For much of the twentieth century, historians posited that technological innovation was primarily the result of individual genius—visionaries whose singular insights propelled society forward. According to this perspective, figures such as Edison or Curie were exceptional not only in intellect but also in their capacity to revolutionize entire fields independently. However, recent scholarship challenges this narrative by emphasizing the collaborative and cumulative nature of scientific advancement. Rather than attributing progress to isolated brilliance, contemporary historians argue that technological breakthroughs often emerge from networks of contributors, institutional support, and the gradual refinement of prior discoveries. Thus, while the myth of the lone inventor persists, the evidence increasingly points to a more collective process underlying innovation.</t>
+          <t>In paleoclimatology, ice cores are often treated as chronological archives: layers of snow compact into ice, trapping gases that later reveal past atmospheres. Accordingly, many reconstructions proceed by assuming that each sampled depth corresponds to a particular time interval, with errors minimized through improved dating models. Yet this assumption becomes fragile when researchers confront diffusion—the gradual spreading of trapped gases after deposition. As a result, the signal at a given depth may reflect not only the local conditions but also the timing of transport within the firn. Consequently, some scholars argue that the record should be read less as a direct transcript and more as a transformed message, requiring deconvolution of the physical processes that shape it.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>How does the passage structure its argument regarding technological innovation?</t>
+          <t>Which choice best describes the passage’s overall organization?</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>By contrasting the traditional view with more recent scholarly perspectives.</t>
+          <t>It explains a common method for interpreting ice-core data, then identifies a specific complication that undermines that method, and finally presents an alternative way scholars recommend reading the record.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>By listing examples of individual inventors who have changed history.</t>
+          <t>It compares two competing interpretations of ice cores, then provides evidence for one interpretation by detailing how diffusion alters gas signals, and concludes by rejecting the other interpretation.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>By explaining the scientific method and its impact on innovation.</t>
+          <t>It introduces diffusion as a general phenomenon, then defines chronological archives in paleoclimatology, and concludes by arguing that dating models are unnecessary.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>By providing statistical data to support a collaborative approach to innovation.</t>
+          <t>It argues that ice-core reconstructions rely on a single assumption, then lists multiple ways researchers can avoid diffusion, and ends by claiming that the record remains a direct transcript of past atmospheres.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,14 +881,14 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>The passage is structured to present a contrast between the traditional view that technological innovation is due to individual genius and the more recent perspective emphasizing collaboration and cumulative progress.</t>
+          <t>The passage first describes how ice cores are used as chronological archives and how reconstructions assume depth corresponds to time. It then explains why that assumption is fragile due to diffusion. Finally, it concludes that scholars recommend reading the record as a transformed message requiring deconvolution.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>686f746a-444e-412c-af99-9bbb7bfb0bca</t>
+          <t>1e2deace-4da8-445c-b9fa-ec6da6083fc2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -896,52 +908,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Text 1: Some historians argue that the invention of the printing press in the fifteenth century was the most important event in spreading new ideas across Europe. They claim that printed books allowed information to travel quickly and reach a much larger audience than handwritten manuscripts ever could. 
-Text 2: While the printing press certainly made books more available, others note that literacy rates remained low for many years after its invention. These historians suggest that teachers and public readings played an equally important role in sharing knowledge, especially among people who could not read.</t>
+          <t>Text 1: In many cities, public libraries began as quiet rooms for reading. Over time, librarians added workshops, story hours, and community meetings. Some people argue that these changes dilute the library’s original purpose. They claim a library should mainly provide books, not programs.
+Text 2: Yet a library’s purpose can shift without disappearing. When librarians host story hours, they still center reading, but they extend it to children who may not visit on their own. Workshops and meetings also help readers find books that match their interests, turning the library into a guide rather than a storehouse. In this way, programs function as a bridge to the same goal: supporting literacy.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>How do Text 1 and Text 2 differ in their perspectives on the impact of the printing press on the spread of knowledge?</t>
+          <t>How does Text 2 respond to the concern raised in Text 1 about changes to public libraries?</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Text 1 emphasizes the role of the printing press in increasing access to information, while Text 2 argues that other methods were equally important.</t>
+          <t>Text 2 argues that the added programs in libraries eliminate the original purpose of providing books.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Text 1 claims that the printing press hindered the spread of knowledge, while Text 2 believes it was the sole reason for increased literacy.</t>
+          <t>Text 2 contends that the programs in libraries shift the purpose but still support the same underlying goal of literacy.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Text 1 suggests that the printing press was less effective than handwritten manuscripts, while Text 2 highlights its superiority.</t>
+          <t>Text 2 suggests that libraries should stop offering community meetings because they discourage reading.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Text 1 and Text 2 both agree that the printing press was the only factor in spreading knowledge widely.</t>
+          <t>Text 2 claims that librarians added programs only to replace books with other forms of entertainment.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Text 1 asserts the printing press was crucial in spreading ideas due to its ability to reach a larger audience, while Text 2 acknowledges its role but also emphasizes the importance of teachers and public readings, contrasting the singular focus of Text 1.</t>
+          <t>Text 1 worries that workshops and story hours dilute the library’s original purpose. Text 2 replies that programs can change how the goal is achieved while still centering reading and literacy, describing programs as a bridge to the same objective.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8aafc6c0-6ad5-47cb-a04e-b56496770eda</t>
+          <t>9be77b39-589d-42ef-86e7-5bbee8e68ae4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,62 +963,61 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cross-Text</t>
+          <t>Words in Context</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Text 1: Historians often argue that technological innovation is the primary driver of societal change, asserting that advancements such as the printing press or the steam engine directly reshape cultural and economic systems. They contend that these inventions create new opportunities, alter communication, and redefine social roles. 
-Text 2: While technological innovation undeniably influences society, some scholars emphasize the reciprocal nature of this relationship. They suggest that social needs and cultural values frequently guide which inventions are developed and adopted, indicating that society itself can shape the trajectory and impact of technological progress.</t>
+          <t>In many museums, labels do more than describe objects; they guide visitors’ attention. A curator might note that a painting uses “muted” colors. The word muted suggests that the colors are not bright or loud. Nearby, the label may mention gray-blue shadows and softened edges. Because these details point to the same idea, a reader can infer what muted means even without a dictionary. However, if the label also says the scene feels “calm,” the meaning becomes even clearer: muted colors often create a quiet mood. In this way, word choice works with description to shape understanding.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>How do Text 1 and Text 2 differ in their views on the role of technological innovation in societal change?</t>
+          <t>In the passage, the word "muted" most nearly means—</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Text 1 sees technology as the sole driver of societal change, while Text 2 suggests society also influences technology.</t>
+          <t>bright and attention-grabbing</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Text 1 claims technology is unimportant, whereas Text 2 sees it as the main factor in societal evolution.</t>
+          <t>not bright or loud</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Text 1 and Text 2 agree that technology only reshapes economic systems, not cultural systems.</t>
+          <t>highly detailed and textured</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Text 1 and Text 2 both argue that technology has no significant impact on societal structures.</t>
+          <t>moving quickly across the canvas</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Text 1 argues that technological innovation is the primary driver of societal change, whereas Text 2 suggests that societal needs and values also play a role in shaping technological progress.</t>
+          <t>The passage states that the word "muted" suggests colors are not bright or loud, and it reinforces this with nearby details like gray-blue shadows and softened edges.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eb02ac38-98ec-4566-8bb6-81d2f8e716f4</t>
+          <t>26c7033c-daea-46a3-b497-949a4b8b662d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,45 +1027,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cross-Text</t>
+          <t>Words in Context</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Text 1: The historian argues that technological innovation invariably follows societal need, positing that necessity acts as the primary catalyst for invention. Citing examples such as the steam engine and the printing press, the author emphasizes a linear progression from problem to solution, suggesting that invention is fundamentally reactive in nature.
-Text 2: In contrast, the sociologist contends that invention often precedes and shapes societal need, noting that the adoption of new technologies can generate unanticipated demands and cultural shifts. By referencing the smartphone’s evolution, the author illustrates how invention can be proactive, fundamentally altering what societies perceive as essential.</t>
+          <t>In many museums, visitors are encouraged to slow down and observe details. A curator might describe a painting as “layered,” meaning that thin coats of color sit on top of one another. This layering matters because it changes how light reflects from the surface. When light hits the upper paint, some colors appear brighter, while others seem deeper. Over time, the top layers can also darken slightly, which may make the image look less vivid than when it was first finished. Thus, the word “layered” is not just a description of order; it is a clue to how the artwork will look.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>What is the primary difference in how the historian and the sociologist view the relationship between technological innovation and societal need?</t>
+          <t>In the passage, the word “layered” most nearly means</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The historian believes technology is always a response to societal needs, while the sociologist believes technology can also create new needs.</t>
+          <t>arranged in thin layers on top of one another</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>The historian argues that societal needs are shaped by technology, whereas the sociologist suggests technology is shaped by societal demands.</t>
+          <t>painted in a single thick coat</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>The historian sees technological innovation as a linear process, while the sociologist views it as unpredictable and chaotic.</t>
+          <t>protected by a clear covering added later</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>The historian and the sociologist both agree that technological innovation is primarily driven by economic factors.</t>
+          <t>displayed in a sequence of different paintings</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1064,445 +1074,447 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Text 1 describes the historian's view that invention is reactive and follows societal need. Text 2 contrasts this by presenting the sociologist's view that invention can be proactive, creating new societal needs. Thus, option A captures this primary difference.</t>
+          <t>The passage defines “layered” as “thin coats of color sit on top of one another,” and it explains that this layering affects how light reflects and how the image changes over time.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>d0b8ef37-0ab4-40b7-987c-0b422726bcea</t>
+          <t>f7fceb53-60ec-4d37-8a86-8e1faec93d91</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Information and Ideas</t>
+          <t>Craft and Structure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central Idea</t>
+          <t>Words in Context</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Throughout history, the invention of tools has shaped human civilization. Early humans used simple stones to hunt animals and prepare food, which made daily survival easier. Over time, people developed more advanced tools, such as metal plows and wheels, leading to increased food production and the growth of communities. These innovations show that tools have always played a key role in helping societies progress and solve challenges.</t>
+          <t>In the early twentieth century, museums often treated artifacts as silent witnesses: objects were displayed to preserve “what had been.” Yet curators who studied how visitors actually learned began to emphasize a different function. They argued that labels and arrangement do not merely record facts; they frame interpretation. A marble statue, for example, can be presented as evidence of artistry or as a token of political power, depending on which details are highlighted. This shift depended on a single premise: meaning is not inherent in materials alone but emerges through context. Consequently, the most “accurate” exhibit is not the one with the most information, but the one that connects information to a clear claim.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Which choice best states the main idea of the passage?</t>
+          <t>In the passage, in the sentence “labels and arrangement do not merely record facts; they frame interpretation,” the word “frame” most nearly means</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The invention of tools began with the use of simple stones.</t>
+          <t>set boundaries around an object’s physical display</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Early communities grew due to increased food production.</t>
+          <t>shape how an audience understands the information</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Tools have been essential in the progress and problem-solving of human societies.</t>
+          <t>protect facts from being misunderstood by visitors</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Metal plows and wheels were significant advancements in history.</t>
+          <t>catalog artifacts according to their original materials</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>The passage discusses how the invention and development of tools have consistently played a crucial role in shaping human civilization, supporting societies in overcoming challenges and advancing. This is the central idea around which the passage is structured, with examples provided to illustrate this key role of tools throughout history.</t>
+          <t>The passage states that labels and arrangement do not simply record facts; instead, they “frame interpretation,” meaning they influence how visitors understand what they see—such as whether a statue is presented as artistry or political power. Option A is about physical display, C is about preventing misunderstanding, and D is about cataloging materials; none matches the passage’s focus on shaping interpretation.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31acd2c0-30d8-4bb4-ae2f-a83995117484</t>
+          <t>6580bff1-3c65-4afb-b753-b3e93c51785c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information and Ideas</t>
+          <t>Craft and Structure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central Idea</t>
+          <t>Words in Context</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>In the early twentieth century, city planners faced the challenge of accommodating rapidly growing populations. They introduced zoning laws, which divided urban areas into sections for residential, commercial, and industrial use. This approach aimed to reduce overcrowding and improve living conditions by separating factories from homes. Over time, these regulations also influenced the shape of neighborhoods and the availability of public spaces, ultimately transforming the way cities developed.</t>
+          <t>In early modern natural philosophy, “heat” was treated less as a measurable substance than as a condition that could be inferred from effects. When an iron bar cooled, its capacity to warm surrounding materials diminished; the change was therefore read as evidence of altered internal state rather than as the loss of a stored material. Yet the same framework also encouraged imprecision: because observers relied on sensory outcomes—temperature, texture, or rate of melting—they could mistake correlation for mechanism. The later shift toward calorimetry did not merely add instruments; it narrowed what counted as an explanation. By separating observable quantities from interpretive claims, scientists replaced conjecture with reproducible procedure.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Which choice best states the main idea of the passage?</t>
+          <t>In the passage, the word "imprecision" most nearly means ____.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>City planners in the early twentieth century faced challenges due to rapidly growing populations.</t>
+          <t>careful measurement that reduces error</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Zoning laws were introduced to separate residential, commercial, and industrial areas in cities.</t>
+          <t>erroneous inference in which correlation is mistaken for the cause</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>The introduction of zoning laws transformed urban development by reducing overcrowding and improving living conditions.</t>
+          <t>the tendency to rely on intuition rather than observation</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Public spaces became more available as a result of zoning regulations.</t>
+          <t>the gradual improvement of instruments over time</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>The passage discusses how early twentieth-century city planners introduced zoning laws to address the challenges of rapid urban population growth. The laws aimed to improve living conditions by separating different types of urban areas and ultimately influenced urban development, aligning with option C as the main idea.</t>
+          <t>The passage says the framework “encouraged imprecision” because observers “could mistake correlation for mechanism.” That means their inferences about cause were flawed: they treated an observed association as if it revealed the underlying mechanism.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fd9bf197-8f2a-4e8a-9857-783fbb15b6eb</t>
+          <t>43aaf5f9-eb1c-42fd-93c5-869793ebb453</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information and Ideas</t>
+          <t>Craft and Structure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central Idea</t>
+          <t>Text Structure</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Throughout the 19th century, urban centers in the United States experienced rapid population growth, largely driven by industrialization and the influx of immigrants seeking economic opportunity. This expansion, however, placed immense strain on municipal infrastructure, resulting in overcrowded housing and inadequate sanitation. In response, reformers advocated for public health measures, such as improved sewage systems and the establishment of sanitation departments. While these interventions faced resistance due to their costs and the disruption of established routines, they ultimately laid the groundwork for modern urban planning by highlighting the necessity of coordinated efforts to address the challenges of burgeoning cities.</t>
+          <t>In many cities, public libraries began as quiet reading rooms, built to protect books and encourage study. Over time, however, librarians noticed that learning often happens through conversation. For example, they organized story hours and small discussion groups, so visitors could share questions as well as answers. Nevertheless, a library’s role is not limited to hosting events. Instead, it also provides access—through books, computers, and trained staff—so people can pursue their own interests. As a result, the library shifts from a place that only stores knowledge to a place that helps people use it. In this way, the library’s purpose becomes both educational and practical.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Which choice best states the main idea of the passage?</t>
+          <t>Which choice best describes the passage’s overall organization?</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Urban centers in the 19th century faced issues due to immigrant influx.</t>
+          <t>It explains how public libraries changed over time by moving from quiet reading rooms to interactive learning spaces, then concludes by summarizing the library’s broader purpose.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Reformers improved sewage systems and sanitation departments.</t>
+          <t>It argues that libraries should focus mainly on events, using examples of story hours and discussion groups to support that claim, and ends by listing specific services.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>The growth of urban centers in the 19th century led to infrastructure challenges and reform efforts that paved the way for modern urban planning.</t>
+          <t>It compares libraries to other community institutions, describing similarities and differences, and then provides a historical timeline of specific library developments.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Industrialization was the primary cause of urban population growth in the 19th century.</t>
+          <t>It presents a problem with traditional libraries, shows that story hours solve the problem, and then argues that trained staff replace books as the primary resource.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>The passage discusses the rapid population growth in urban centers due to industrialization and immigration, the resulting strain on infrastructure, and the reform efforts that followed, highlighting the central idea of how these developments contributed to modern urban planning.</t>
+          <t>The passage first describes libraries’ original purpose (quiet reading rooms), then shows an evolution toward conversation-based learning (story hours and discussion groups). It follows with a contrast (“Nevertheless”) to emphasize that libraries also provide access to resources for self-directed interests, and it ends by summarizing the resulting purpose as both educational and practical.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>98e258b0-4ca1-4e8b-a6f1-6bb941eca292</t>
+          <t>ed37bfa7-2a70-4118-b65b-927ba9deea11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information and Ideas</t>
+          <t>Craft and Structure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Command of Evidence</t>
+          <t>Text Structure</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>In the early 1900s, scientists began to notice that honeybee populations were declining in certain areas. Some researchers suggested that new farming methods, including increased use of pesticides, might be responsible for the drop in bee numbers. Others pointed to changes in weather patterns as a possible cause. However, a study published in 1925 found that bee colonies near farms using few chemicals remained healthy, while those close to heavily treated fields experienced sharp declines. This led many to believe that pesticide use was a major factor in the reduction of honeybee populations.</t>
+          <t>In environmental policy, impact assessments are often described as neutral summaries of evidence. They may list projected temperatures, forecasted emissions, and potential effects on water quality, giving readers the impression that decision-making follows automatically from data. However, the structure of these reports complicates that assumption. For instance, when authors group uncertainty under headings like “limitations,” they can frame doubt as a peripheral issue rather than as a core feature of the model. Moreover, the sequence of topics—beginning with ecological outcomes and ending with economic considerations—guides attention toward some trade-offs while downplaying others. Thus, although impact assessments present themselves as descriptive, their organization functions rhetorically, shaping what counts as significant.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Which detail from the passage best supports the conclusion that pesticide use was a major factor in the reduction of honeybee populations?</t>
+          <t>Which choice best describes the rhetorical move the passage makes as it progresses from describing impact assessments to arguing that their organization shapes judgment?</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Scientists in the early 1900s noticed a decline in honeybee populations in certain areas.</t>
+          <t>It begins by challenging the claim that impact assessments are neutral, then provides specific examples of how report sections and topic order influence how readers interpret uncertainty and trade-offs.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Some researchers suggested that new farming methods could be responsible for the drop in bee numbers.</t>
+          <t>It starts with a definition of impact assessments, then shifts to a historical overview before concluding with a general recommendation for improving report transparency.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A study found that bee colonies near farms using few chemicals remained healthy, while those near heavily treated fields experienced declines.</t>
+          <t>It introduces the main idea that impact assessments rely on data, then contrasts that approach with unrelated fields and ends by stating that the evidence is ultimately conclusive.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Others pointed to changes in weather patterns as a possible cause for the decline.</t>
+          <t>It outlines multiple viewpoints on environmental policy, then uses statistical evidence and case studies to prove that uncertainty is always peripheral to modeling.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Option C provides the strongest and most direct evidence supporting the conclusion that pesticide use was a major factor in the reduction of honeybee populations, as it describes the study's findings correlating pesticide use with declines in bee colonies.</t>
+          <t>The passage first says impact assessments appear neutral, then undermines that assumption by explaining how headings (e.g., “limitations”) and the sequence of topics rhetorically shape what readers see as significant.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ab43c827-d23b-4108-8f11-2c47b4bce9c6</t>
+          <t>b1d3bb9e-2d0e-4db1-bc70-4188a6fd3bfe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information and Ideas</t>
+          <t>Craft and Structure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Command of Evidence</t>
+          <t>Text Structure</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>In the early twentieth century, city planners began to recognize the importance of public parks for urban communities. Reports from the period noted that green spaces contributed to improved air quality and provided residents with areas for recreation and socialization. Some officials argued that parks encouraged healthier lifestyles by offering opportunities for exercise. However, critics maintained that the cost of maintaining such spaces was burdensome for municipal budgets. Despite these concerns, the number of public parks in major cities increased steadily between 1900 and 1930, suggesting that their perceived benefits outweighed financial objections.</t>
+          <t>In the early twentieth century, scholars treated climate as a backdrop: a relatively stable set of conditions that shaped where people could farm or build. From that view, weather records mattered mainly because they confirmed how environments constrained behavior. However, recent historians argue that this framing underestimates the role of prediction. When institutions began to forecast rainfall and temperature, climate became an active target of policy, not merely an influence on it. Consequently, the language of probability entered public planning, and uncertainty was managed through categories such as “normal” seasons and “abnormal” deviations. In other words, the shift from description to prediction transformed climate into a tool for governance, reshaping both scientific practice and civic expectations.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Which detail from the passage best supports the conclusion that public parks were valued despite their costs?</t>
+          <t>Which choice best describes the passage’s overall structure?</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Reports noted that green spaces contributed to improved air quality.</t>
+          <t>It presents an initial historical view, contrasts it with a newer argument, and then explains the consequences of the newer framing.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Officials argued that parks encouraged healthier lifestyles.</t>
+          <t>It defines climate, provides multiple examples of how it affects daily life, and concludes with a call for future research.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Critics maintained that the cost of maintaining parks was burdensome.</t>
+          <t>It argues that weather records are unreliable, supports that claim with evidence from institutions, and then refutes a counterargument.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>The number of public parks in major cities increased steadily between 1900 and 1930.</t>
+          <t>It traces the history of climate science chronologically from early twentieth-century scholarship to modern civic planning, without making a clear comparison.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Option D provides direct evidence that the perceived benefits of public parks were valued over the financial concerns, as indicated by the steady increase in their number despite cost criticisms.</t>
+          <t>The passage first describes how scholars previously treated climate as a backdrop, then contrasts that view with historians who argue that prediction plays a larger role. It follows by explaining how forecasting changed climate into a tool of governance and what that changed in both science and civic expectations.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e18ed099-f07b-4c69-afeb-829d5101f483</t>
+          <t>72fdcfdf-52b9-47ca-9d2f-41427d8c8c03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Information and Ideas</t>
+          <t>Craft and Structure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Command of Evidence</t>
+          <t>Cross-Text</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The migration of monarch butterflies has long fascinated scientists due to its extraordinary scale and navigational precision. Recent studies suggest that these insects rely on a combination of environmental cues, such as the angle of sunlight and Earth's magnetic field, to guide their journey over thousands of kilometers. While some researchers argue that genetic predisposition alone could account for this behavior, others point to experiments in which monarchs exposed to altered light conditions deviated significantly from their typical migratory paths. Moreover, monarchs raised in captivity and released into the wild often fail to complete migration, implying that both innate and learned factors contribute to successful navigation.</t>
+          <t>Text 1: In many cities, public libraries began as quiet rooms for reading. Over time, they added computers, recording studios, and makerspaces. Some people argue that these changes distract from the library’s original purpose: helping people read books. They point to the noise that can come with group projects and say that technology should be kept in separate places.
+Text 2: A different view is that libraries still center on reading, but reading can include new forms. When students edit podcasts or design simple robots, they must research, plan, and communicate their ideas clearly. In this way, the library’s tools do not replace literacy; they extend it to audiences who learn through sound, images, and hands-on work. Noise, supporters add, often signals active learning rather than disorder.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Which detail from the passage best supports the conclusion that both innate and learned factors contribute to successful monarch butterfly navigation?</t>
+          <t>The relationship between Text 1 and Text 2 is best described as</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Monarch butterflies rely on a combination of environmental cues for navigation.</t>
+          <t>Text 1 warns that adding technology can distract from reading and that technology should be kept in separate places, while Text 2 responds that reading can include new forms and that library tools extend literacy.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Some researchers argue that genetic predisposition alone could account for migratory behavior.</t>
+          <t>Text 1 claims libraries have always included technology, while Text 2 argues that libraries should return to being silent.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Monarchs exposed to altered light conditions deviated from their typical migratory paths.</t>
+          <t>Text 1 focuses on how libraries started, while Text 2 focuses on how libraries will change in the future.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Monarchs raised in captivity and released into the wild often fail to complete migration.</t>
+          <t>Text 1 and Text 2 agree that technology distracts from reading but disagree about whether noise is harmful.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Option D directly supports the conclusion by providing evidence that monarchs raised in captivity, which likely lack learned experience, often fail to complete migration, indicating that both innate and learned factors are important.</t>
+          <t>Text 1 expresses concern that added technology and its associated noise distract from the library’s purpose of helping people read books, and it argues that technology should be kept in separate places. Text 2 presents a counterargument: libraries still center on reading, and reading can take new forms through tools like podcasts and robotics. The other choices either misstate Text 1’s position or describe differences not supported by the texts.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49914cbc-7026-49d1-a15d-e8720fe90277</t>
+          <t>9b461965-780a-470f-bc4e-ba22549c1018</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information and Ideas</t>
+          <t>Craft and Structure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inference</t>
+          <t>Cross-Text</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>During the late 1800s, many families in rural areas depended on wells for their water supply. These wells were often dug by hand and lined with stones to prevent collapse. In periods of heavy rainfall, the water in the wells would rise, sometimes reaching near the surface. When droughts occurred, however, some wells would dry out completely, forcing families to travel long distances to find water elsewhere.</t>
+          <t>Text 1: In studies of urban heat islands, researchers often emphasize nighttime conditions: paved surfaces store solar energy and release it after sunset, raising local temperatures even when daytime weather is mild. Because this pattern is consistent across many cities, some reports treat nighttime readings as a reliable proxy for overall heat exposure. Yet residents experience discomfort over the full day, suggesting that a single temporal focus may compress different heat mechanisms into one measure.
+Text 2: A different approach separates heat effects by time. Instead of assuming nighttime dominance, planners compare daytime shading, wind-driven cooling, and nighttime radiation from building materials. They find that neighborhoods with similar evening temperatures can differ sharply in afternoon heat stress, particularly where trees reduce direct sun. By reallocating attention from stored heat to concurrent processes, the study revises the earlier claim: nighttime data are informative, but they do not by themselves represent the lived pattern of exposure.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>What can be most reasonably inferred about the challenges faced by rural families relying on wells during the late 1800s?</t>
+          <t>In comparing the claims about using nighttime readings, how does Text 2 relate to Text 1?</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>They often had to find alternative water sources during dry periods.</t>
+          <t>Text 2 challenges Text 1’s reliance on nighttime readings as a reliable proxy by arguing that daytime processes can produce different heat stress patterns.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>They primarily relied on rainwater for their wells.</t>
+          <t>Text 2 fully supports Text 1 by confirming that nighttime conditions reliably capture residents’ full-day discomfort.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>They had no issues accessing water throughout the year.</t>
+          <t>Text 2 adds new evidence that nighttime and daytime effects are identical across all neighborhoods.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>They frequently moved to new locations due to water scarcity.</t>
+          <t>Text 2 argues that nighttime data are unrelated to heat exposure and should be excluded from studies.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1512,61 +1524,64 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>The passage discusses how wells could dry out during droughts, forcing families to travel for water, suggesting they faced challenges in accessing water.</t>
+          <t>Text 1 says researchers often treat nighttime readings as a reliable proxy for overall heat exposure, but also notes that residents experience discomfort over the full day. Text 2 revises that earlier claim: it says nighttime data are informative, yet they do not by themselves represent the lived pattern of exposure. It also shows that similar evening temperatures can coincide with different afternoon heat stress, indicating that relying on nighttime alone can miss other processes—supporting option A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8c23571a-fe2c-4f70-8af2-4dab6b08525b</t>
+          <t>ad124191-1ef5-44d3-ae45-987381401d6f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Information and Ideas</t>
+          <t>Craft and Structure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inference</t>
+          <t>Cross-Text</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>In the early decades of the twentieth century, many rural communities in the United States lacked access to electricity, while urban centers rapidly adopted electric lighting and appliances. Although federal initiatives to expand electrical infrastructure began in the 1930s, some isolated towns did not receive consistent service until years later. During this period, rural households often relied on kerosene lamps for lighting and performed household tasks manually, even as urban families increasingly benefited from electric conveniences.</t>
+          <t>Text 1
+In the study of language change, some scholars argue that sound shifts proceed almost mechanically once a community adopts a new pronunciation habit. They point to regularities—certain vowels moving in parallel directions—and treat these patterns as evidence that speakers do not deliberately steer outcomes. On this view, variation is primarily a byproduct of social mixing, with grammar and meaning remaining comparatively stable.
+Text 2
+Other researchers accept the existence of recurring sound patterns but contest the claim that change is directionless. They note that communities often reorganize pronunciation to preserve distinctions that matter for meaning, especially when contact between groups increases ambiguity. Thus, even when shifts look “mechanical” in the short term, long-term trends reveal strategic constraints: speakers maintain contrast, and the resulting regularities can be read as the linguistic system adapting to communicative pressure rather than drifting solely from habit.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Which inference is best supported by the passage?</t>
+          <t>Which statement best describes how Text 2 responds to Text 1’s claim that sound shifts proceed almost mechanically and are not deliberately steered by speakers?</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Rural communities were quick to adopt electricity once it became available.</t>
+          <t>Text 2 largely agrees with Text 1’s mechanical account, adding only that some short-term shifts may appear to involve strategic constraints.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>The federal initiatives of the 1930s immediately resolved the lack of electricity in rural areas.</t>
+          <t>Text 2 argues that, unlike Text 1 claims, grammar and meaning change rapidly whenever sound shifts occur.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>The delay in receiving electricity limited technological and household conveniences in rural areas compared to urban ones.</t>
+          <t>Text 2 challenges Text 1 by rejecting the idea that speakers do not steer outcomes, arguing instead that communicative pressure can constrain how shifts develop.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Urban families did not benefit from electrical conveniences until the 1930s.</t>
+          <t>Text 2 supports Text 1 by presenting additional evidence that social mixing is the only cause of linguistic variation.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1576,14 +1591,14 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>The passage discusses the difference in access to electricity between urban and rural areas, with rural households relying on manual methods due to delayed service. This suggests that the lack of electricity limited their access to conveniences that urban families enjoyed.</t>
+          <t>Text 1 claims sound shifts proceed “almost mechanically” and that speakers do not deliberately steer outcomes, with grammar and meaning remaining comparatively stable. Text 2 accepts recurring sound patterns but explicitly contests the idea that change is directionless: it argues that communities reorganize pronunciation to preserve meaning distinctions and that long-term trends reflect strategic constraints shaped by communicative pressure. This directly challenges Text 1’s claim about whether speakers steer outcomes.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ca57c8bf-63ed-4c01-bd5f-5f6351325bad</t>
+          <t>0c2da2af-9fc6-4b7c-9375-ff221310cdec</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1593,61 +1608,61 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inference</t>
+          <t>Central Idea</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>During the late nineteenth century, urban centers in the United States experienced a marked increase in population density, a trend often attributed to waves of immigration and internal migration from rural areas. Despite the proliferation of tenement housing designed to accommodate this influx, contemporary accounts describe persistent overcrowding and unsanitary conditions. Municipal governments responded by enacting building codes and sanitation reforms, yet reports of high rates of infectious disease persisted into the early twentieth century. These patterns suggest that the measures implemented, while perhaps well-intentioned, were insufficient to fully address the public health challenges posed by rapid urbanization.</t>
+          <t>In many coastal cities, planners use tide charts to schedule daily work. Tide charts show how sea level changes over time, so workers can predict when water will be higher or lower. This information helps crews move boats safely, because launching and docking are easiest when the water is deep enough. It also affects road maintenance, since flooding risk rises during high tides. By using the charts, cities can coordinate activities across different locations and reduce delays caused by unexpected water levels. Overall, tide charts guide practical decisions by linking the timing of work to predictable changes in sea level.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Which inference is best supported by the passage?</t>
+          <t>Which choice best states the central idea of the passage?</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>The building codes and sanitation reforms had no positive impact on urban living conditions.</t>
+          <t>Tide charts are useful because they help coastal cities time work activities by predicting predictable changes in sea level.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Urban centers in the United States struggled to maintain adequate public health standards despite efforts to improve conditions.</t>
+          <t>Tide charts mainly improve safety by determining when sea level will be deep enough for boats to launch and dock.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>The high rates of infectious disease were primarily caused by the waves of immigration.</t>
+          <t>Tide charts are valuable primarily for reducing flooding during high tides by helping cities schedule road maintenance.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Municipal governments were unaware of the public health challenges during rapid urbanization.</t>
+          <t>Tide charts are effective only when coastal cities coordinate work across locations, since coordination prevents all delays caused by sea level changes.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>The passage discusses the implementation of building codes and sanitation reforms in response to overcrowding and unsanitary conditions. Despite these efforts, reports of high rates of infectious disease persisted, indicating that maintaining adequate public health standards was a struggle.</t>
+          <t>The passage presents tide charts as a tool for scheduling daily work by predicting sea level changes. It explains multiple applications—safe boat handling, road maintenance related to flooding risk, and coordinating activities to reduce delays—supporting the broader central claim that tide charts guide practical decisions through predictable timing.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>b5ff952b-1c49-4cc6-8c70-097f99227959</t>
+          <t>6fe2031e-61c1-42c1-9d90-c36e98fbf104</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1657,44 +1672,44 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Data Interpretation</t>
+          <t>Central Idea</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A study of two local parks tracked the number of visitors during the summer months. Park A received an average of 200 visitors each day in June, 250 visitors per day in July, and 300 visitors per day in August. Park B, in contrast, had 150 visitors per day in June, 180 per day in July, and 170 per day in August. Overall, Park A saw a steady increase in visitors over the summer, while Park B experienced a slight rise in July followed by a decrease in August.</t>
+          <t>In the 1970s, several urban planners began using “impact assessments” to anticipate how proposed projects would affect neighborhoods. These assessments required more than listing costs and benefits; they also asked planners to consider secondary effects such as changes in housing availability, commuting patterns, and local business revenue. When a highway expansion was evaluated under this framework, analysts modeled potential displacement from rising rents and then estimated how displacement might reduce customer traffic for nearby stores. In contrast, an earlier review of the same proposal had focused mainly on traffic flow and construction expenses. The later method did not guarantee a different decision, but it changed what information counted as relevant to the project’s overall consequences.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>According to the passage, which statement is most supported by the data regarding visitors to the parks during the summer months?</t>
+          <t>Which choice best states the main purpose of the passage?</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Park A consistently had more visitors than Park B in each summer month.</t>
+          <t>To explain how impact assessments broadened the range of factors urban planners considered when evaluating proposed projects</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Park B had the highest number of visitors in August.</t>
+          <t>To argue that highway expansions should be rejected whenever they lead to any displacement of residents</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Both Park A and Park B had the same number of visitors in July.</t>
+          <t>To show that modeling displacement and customer traffic is more accurate than traditional traffic-flow analysis</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Park B experienced a steady increase in visitors throughout the summer.</t>
+          <t>To compare construction costs of highway projects across different time periods</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1704,14 +1719,14 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>The data shows that Park A had more visitors in every month: 200 vs 150 in June, 250 vs 180 in July, and 300 vs 170 in August. This supports option A. Option B is incorrect because Park B's visitors decreased in August. Option C is incorrect because they had different visitor numbers in July. Option D is incorrect because Park B's numbers decreased in August.</t>
+          <t>The passage contrasts earlier reviews that emphasized costs and traffic flow with later impact assessments that also required considering secondary effects like housing availability, commuting patterns, and local business revenue. The key takeaway is the shift in what information was considered relevant—not that decisions always change, that one method is always more accurate, or that costs are compared.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>d72e085f-817c-4265-a197-6515d3e9b2e9</t>
+          <t>ee37cc76-0481-4830-80cd-c9037f33ab09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1721,61 +1736,61 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Data Interpretation</t>
+          <t>Central Idea</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>A recent survey of 1,000 city residents found that 58% reported using public transportation at least three times per week, while 28% said they rarely or never used it. Among those who used public transportation frequently, 64% expressed satisfaction with the current system, compared to only 35% satisfaction among infrequent users. Over the past five years, the proportion of frequent users has increased by 15 percentage points, while overall satisfaction with public transportation has risen by 10 percentage points during the same period.</t>
+          <t>In early experiments on plant growth, researchers compared seedlings placed in identical containers but exposed to different light spectra. When red wavelengths dominated, leaves expanded rapidly, yet the rate at which stems thickened lagged. When blue wavelengths dominated, stem thickening increased, but overall leaf area grew more slowly. To test whether these outcomes reflected a single limitation, scientists measured two internal signals: one associated with cell expansion and another associated with cell division. Across treatments, the expansion signal rose in the red-dominant condition, while the division signal rose in the blue-dominant condition. The results suggest that light does not uniformly accelerate growth; instead, different portions of the spectrum shift which cellular process becomes most active, producing distinct growth patterns.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>According to the passage, which statement is most supported by the data regarding public transportation satisfaction among city residents?</t>
+          <t>Which statement best expresses the central claim of the passage?</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>The overall satisfaction with public transportation has surpassed the satisfaction rate among frequent users.</t>
+          <t>Different light spectra affect plant growth by activating different cellular processes, leading to distinct patterns of leaf and stem development.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Frequent users of public transportation are more satisfied with the system than infrequent users.</t>
+          <t>Plant growth is maximized when red and blue wavelengths are both present in equal proportions, since they independently increase leaf area and stem thickness.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>The increase in the proportion of frequent users has not affected overall satisfaction levels.</t>
+          <t>The primary effect of light on seedlings is to speed up cell division, and the observed differences in leaf and stem growth are secondary.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>The majority of infrequent users are satisfied with the current public transportation system.</t>
+          <t>Red wavelengths primarily promote cell division while blue wavelengths primarily promote cell expansion, so each spectrum targets a different stage of the cell cycle.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>The passage states that 64% of frequent users expressed satisfaction with the public transportation system, compared to only 35% satisfaction among infrequent users, supporting the conclusion that frequent users are more satisfied.</t>
+          <t>The passage concludes that light does not uniformly accelerate growth; instead, different wavelengths shift which cellular process (expansion vs. division) becomes most active, producing different growth patterns. Option A synthesizes this claim with the described signal changes and resulting leaf/stem differences. The other options either overgeneralize (B), misidentify the dominant process (C), or reverse/incorrectly assign processes to colors (D).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5be1e9f3-e814-43f7-a327-ff610ac1c1fe</t>
+          <t>afc1574f-a68f-4fd4-834f-3dfb4ab2585b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1785,44 +1800,44 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Data Interpretation</t>
+          <t>Command of Evidence</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>A longitudinal study conducted between 1990 and 2020 tracked literacy rates among adults in Region X and Region Y. In 1990, Region X reported a literacy rate of 72%, while Region Y’s was slightly lower at 68%. By 2005, both regions had improved, with Region X reaching 80% and Region Y increasing to 74%. However, between 2005 and 2020, growth plateaued in Region X, which recorded a marginal rise to 82%, whereas Region Y experienced a more pronounced gain, reaching 81%. Researchers attribute Region Y’s late surge to a comprehensive public education initiative launched in 2010, which Region X did not implement.</t>
+          <t>In 1851, a city library began keeping records of books that were checked out most often. The librarian reported that “popular titles” drew the most readers, but the evidence in the log showed otherwise. For each month, the library noted how many different books were borrowed at least once. In March, 420 different books were borrowed, and 60 of them were checked out more than 10 times. In April, 390 different books were borrowed, and 80 of them were checked out more than 10 times. The librarian concluded that the library’s readers preferred a wider range of books in March than in April, even though both months had many repeat borrowers.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Which choice best describes what the reported data shows about the literacy rates in Regions X and Y from 1990 to 2020?</t>
+          <t>Which detail from the library’s records most strongly supports the librarian’s conclusion that readers preferred a wider range of books in March than in April?</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Region X consistently had a higher literacy rate than Region Y throughout the period.</t>
+          <t>In March, 420 different books were borrowed.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Region Y surpassed Region X in literacy rate by 2020 due to its public education initiative.</t>
+          <t>In April, 390 different books were borrowed.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Both regions started with similar literacy rates but diverged significantly by 2020.</t>
+          <t>In March, 60 books were checked out more than 10 times.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Region X had a rapid increase in literacy rate after 2005, unlike Region Y.</t>
+          <t>In April, 80 books were checked out more than 10 times.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1832,69 +1847,61 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>The data shows that Region X consistently maintained a higher literacy rate than Region Y from 1990 through 2020, even though Region Y had significant gains and nearly caught up by 2020.</t>
+          <t>The conclusion depends on the claim that March had a wider range of books than April. The most direct supporting evidence is that March had more different books borrowed (420) than April (390). The other details concern repeat checkouts and do not directly establish the breadth of the range as clearly as the number of different books.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08a6bb3e-0cec-4375-b601-984b7dd5fbb7</t>
+          <t>ca359f81-5a15-44b5-ab1e-bdd387bd5abc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Standard English Conventions</t>
+          <t>Information and Ideas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boundaries</t>
+          <t>Command of Evidence</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marie Curie conducted groundbreaking research on radioactivity( ) she became the first woman to win a Nobel Prize.</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Marie Curie conducted groundbreaking research on radioactivity( ) she became the first woman to win a Nobel Prize.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>( )</t>
-        </is>
-      </c>
+          <t>In 1912, a city council considered whether to replace its horse-drawn streetcars with electric ones. Proponents argued that electric cars would perform better during bad weather. A mechanical engineer’s report listed two sets of observations: on clear days, electric cars completed the 4-mile route in 14 minutes, while horse-drawn cars took 19 minutes; on rainy days, electric cars averaged 18 minutes, and horse-drawn cars averaged 24 minutes. A separate finance memo noted that installing overhead wiring was expensive, and that maintenance crews would need new training. The council’s final vote cited the engineer’s timing results but did not mention the training requirement.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Which piece of information from the passage best supports the council’s decision, given the proponents’ claim that electric cars would perform better during bad weather?</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>;</t>
+          <t>On clear days, electric cars completed the 4-mile route in 14 minutes, while horse-drawn cars took 19 minutes.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>, and</t>
+          <t>On rainy days, electric cars averaged 18 minutes, while horse-drawn cars averaged 24 minutes.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Installing overhead wiring was expensive, and maintenance crews would need new training.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>but</t>
+          <t>The council’s final vote cited the engineer’s timing results but did not mention the training requirement.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1904,213 +1911,189 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>The sentence contains two independent clauses, so a comma followed by a coordinating conjunction is needed to correctly join them. Option B correctly uses ', and' to connect the two clauses, making it the correct choice.</t>
+          <t>The proponents’ claim is specifically about performance during bad weather (rain). Option B gives the rainy-day timing comparison between electric and horse-drawn cars, showing electric cars complete the route faster than horse-drawn cars on rainy days. Option A addresses clear days, option C concerns cost and training rather than performance in bad weather, and option D describes the council’s action without providing performance evidence.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a2e84a25-c7ee-4215-89bd-c6a01194133d</t>
+          <t>7b9ab154-a40c-496f-a110-c06658954890</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Standard English Conventions</t>
+          <t>Information and Ideas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boundaries</t>
+          <t>Command of Evidence</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>The telescope revealed distant galaxies to astronomers however, further analysis was necessary to understand their composition.</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>The telescope revealed distant galaxies to astronomers however, further analysis was necessary to understand their composition.</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>however,</t>
-        </is>
-      </c>
+          <t>In a study of urban heat, researchers compared “cool-roof” and “standard-roof” buildings over a summer month. On each of 12 days, they recorded roof surface temperature at 3 p.m. and neighborhood air temperature at street level. The cool-roof group showed lower average roof temperatures on 10 of the 12 days, with a mean difference of 6.2°C. However, street-level air temperature was lower in the cool-roof neighborhoods on only 7 of the 12 days, and the mean difference was 1.1°C. The report also notes that wind speed varied: on days when wind was strongest, both roof types had closer surface temperatures, and air temperatures differed less. The authors conclude that cool roofs reduce heat at the roof surface more consistently than they reduce heat in the surrounding air.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Which finding from the study most strongly supports the authors’ conclusion that cool roofs reduce heat at the roof surface more consistently than they reduce heat in the surrounding air?</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>however,</t>
+          <t>Cool-roof buildings had lower average roof surface temperatures on 10 of the 12 days, with a mean difference of 6.2°C.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>however; further</t>
+          <t>Cool-roof neighborhoods had lower street-level air temperatures on 7 of the 12 days, with a mean difference of 1.1°C.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>however further,</t>
+          <t>On days when wind was strongest, both roof types had closer surface temperatures, and air temperatures differed less.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>however. Further</t>
+          <t>The researchers recorded temperatures at 3 p.m. at the roof surface and at street level for 12 days during one summer month.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>The sentence contains two independent clauses that should be correctly separated with a semicolon before the conjunctive adverb 'however' to conform to standard English conventions.</t>
+          <t>The conclusion emphasizes *consistency* at the roof surface compared with the surrounding air. The strongest direct support is that cool roofs showed lower roof surface temperatures on 10 of 12 days (more consistent) and by a larger mean difference (6.2°C). The air-temperature results (7 of 12 days; 1.1°C) support the comparison but are less directly the evidence for “more consistently” at the roof surface.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>e5022311-cf1c-4c24-b42b-a934f609db9f</t>
+          <t>6a4a250b-ad83-47d9-be3b-9135663e30d3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Standard English Conventions</t>
+          <t>Information and Ideas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boundaries</t>
+          <t>Inference</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The paleontologist carefully cataloged each fossil in the collection she recognized that accurate records would be essential for future research.</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>The paleontologist carefully cataloged each fossil in the collection she recognized that accurate records would be essential for future research.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>she recognized that</t>
-        </is>
-      </c>
+          <t>In 2019, a coastal city began using a new system to manage stormwater. The city installed underground pipes to carry runoff away from streets and added gardens that absorb water. After heavy rain, inspectors compared flooded areas with records from the previous year. They found that the number of blocks with standing water decreased, and the time water remained on the surface became shorter. However, officials also reported that the streets near the oldest part of the city still flooded more than other areas, even after the new system was installed. The city concluded that the changes were most effective where the new pipes and gardens were already connected.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Based on the inspectors’ findings and the officials’ conclusion, which inference is most strongly supported?</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>; she recognized that</t>
+          <t>The new stormwater system reduced flooding overall, but it did not fully prevent flooding in every neighborhood.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>, she recognized that</t>
+          <t>The inspectors’ comparisons were flawed because the previous year’s data included unusually severe storms.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>. She recognized that</t>
+          <t>The gardens were more effective than the underground pipes in reducing the duration of standing water.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>: she recognized that</t>
+          <t>Flooding near the oldest part of the city persisted because the new system was never installed there.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>The original sentence contains two independent clauses that need to be correctly separated. A period should be used to separate them, creating two complete sentences: 'The paleontologist carefully cataloged each fossil in the collection. She recognized that accurate records would be essential for future research.'</t>
+          <t>The passage states that after the new system was installed, blocks with standing water decreased and water stayed on the surface for a shorter time. Yet it also says streets near the oldest part of the city still flooded more than other areas. The city concludes the changes were most effective where the pipes and gardens were connected, supporting that effectiveness varied by location rather than that the system completely failed everywhere. Options B and C are not supported by the passage, and D assumes the system was never installed near the oldest part, which the passage does not claim.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13cc2a32-0d52-4ced-8ed9-fe778301ea8b</t>
+          <t>268ca310-108b-4cc9-8d6a-34cdc4e91186</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Standard English Conventions</t>
+          <t>Information and Ideas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Form, Structure, and Sense</t>
+          <t>Inference</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>During the Renaissance, artists developed new techniques that enhanced painting and sculpture, making them more realistic and expressive than those produced in earlier periods.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>During the Renaissance, artists developed new techniques that enhanced painting and sculpture, making them more realistic and expressive than those produced in earlier periods.</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>making them more realistic and expressive than those produced</t>
-        </is>
-      </c>
+          <t>During the late nineteenth century, several coastal cities adopted separate municipal systems for water supply and sewage disposal. In Riverton, the waterworks were expanded first, drawing cleaner water from a distant reservoir. Only after several years did the city install new sewer lines that carried waste away from neighborhoods and into a treatment basin. City records from the same period show that reported cases of a waterborne illness fell sharply soon after the reservoir expansion, but the decline slowed and then continued only after the sewer lines became operational. The timing suggests that improved water access reduced exposure, while later infrastructure reduced contamination from waste that might otherwise reenter local water sources.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Based on the passage, which inference is most strongly supported about why waterborne illness cases fell sharply soon after the reservoir expansion in Riverton?</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>making them more realistic and expressive than those produced</t>
+          <t>Improved water from the distant reservoir reduced residents' exposure to contamination before the sewer lines began operating.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>making them more realistic and expressive than that produced</t>
+          <t>The sewer lines prevented waste from reaching the reservoir, which immediately caused the sharp fall in cases.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>making it more realistic and expressive than those produced</t>
+          <t>The treatment basin began operating at the same time as the reservoir expansion, directly causing the sharp decline.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>making it more realistic and expressive than that produced</t>
+          <t>Reported cases declined because the city changed its reporting practices rather than because contamination decreased.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2120,213 +2103,189 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>The correct choice is 'making them more realistic and expressive than those produced' because 'them' correctly refers to 'painting and sculpture,' and 'those' correctly refers to 'the paintings and sculptures produced in earlier periods.'</t>
+          <t>The passage states that cases fell sharply soon after the reservoir expansion and that improved water access reduced exposure. It also says the sewer lines were installed only after several years, so they could not have immediately caused the initial sharp fall. Options B and C introduce claims about timing the passage does not support, and D contradicts the passage by attributing the change to reporting rather than to reduced contamination or exposure.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>e1a84ef3-219f-4d16-9cd5-2105e9947016</t>
+          <t>f47875db-c498-4459-b38d-be0f85d7f083</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Standard English Conventions</t>
+          <t>Information and Ideas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Form, Structure, and Sense</t>
+          <t>Inference</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>While the artist’s early sculptures were praised for their originality, her later works, which focus on abstract forms, ______ less critical attention.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>While the artist’s early sculptures were praised for their originality, her later works, which focus on abstract forms, ______ less critical attention.</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>has received</t>
-        </is>
-      </c>
+          <t>In a coastal city, officials monitored how two factors affected the number of bird deaths recorded each week. Factor A was the duration of nighttime street lighting, measured in hours. Factor B was the frequency of fog events, counted as the number of days with dense fog. Over one season, the dataset showed that weeks with longer lighting hours often coincided with higher death counts, but this pattern weakened during weeks with many fog days. When fog days were high, changes in lighting hours corresponded to relatively small changes in deaths. Conversely, when fog days were low, variations in lighting hours aligned more consistently with the death counts. These results suggest that one factor conditions the effect of the other rather than both acting independently.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Based on the passage, which inference is most strongly supported?</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>has received</t>
+          <t>Fog events reduce the impact that lighting duration has on weekly bird deaths.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>have received</t>
+          <t>Longer nighttime street lighting always increases bird deaths regardless of fog.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>receives</t>
+          <t>Lighting duration and fog frequency both independently determine bird deaths.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>was receiving</t>
+          <t>Bird deaths are primarily caused by fog events, not by lighting duration.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>The subject 'works' is plural, so the verb should also be in plural form. Therefore, 'have received' is the correct choice for subject-verb agreement.</t>
+          <t>The passage states that the lighting–death relationship is strong when fog days are low but weakens when fog days are high, implying that fog conditions (or diminishes) how much lighting duration affects deaths. The other options contradict the passage’s claim that the factors interact and that the effect changes with fog levels.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cd524534-e24f-4f13-b9de-bd7015c565a0</t>
+          <t>b82a52f7-173c-4383-b34b-257819c52eb6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Standard English Conventions</t>
+          <t>Information and Ideas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Form, Structure, and Sense</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>While the results of the experiment were promising, the researchers agreed that further testing, as well as peer review, __ necessary before drawing definitive conclusions.</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>While the results of the experiment were promising, the researchers agreed that further testing, as well as peer review, __ necessary before drawing definitive conclusions.</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
+          <t>A school tracked how many students arrived on time each week for four weeks. In Week 1, 18 students were on time. In Week 2, 22 students were on time. In Week 3, 20 students were on time. In Week 4, 25 students were on time. The total number of students in the school was the same each week, so the on-time counts can be compared directly. From Week 1 to Week 4, the number of on-time students increased.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Based on the on-time counts, what is the best supported conclusion about the overall change from Week 1 to Week 4?</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>The on-time count increased by 7 students from Week 1 to Week 4.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>The on-time count decreased by 2 students from Week 1 to Week 4.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>The on-time count stayed the same from Week 1 to Week 4.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>The on-time count doubled from Week 1 to Week 4.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>The subject of the verb is 'further testing, as well as peer review,' which is plural, so the correct verb form is 'were.'</t>
+          <t>Week 1 has 18 on-time students and Week 4 has 25 on-time students. The change is 25 − 18 = 7, so the on-time count increased by 7 students. The other options contradict the given counts.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1dc34444-5f0a-4725-b015-a680211f437e</t>
+          <t>d8690b31-5733-47ed-8923-fac7c2e2f521</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Standard English Conventions</t>
+          <t>Information and Ideas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Modifiers</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Walking through the museum, the ancient sculptures fascinated Maria.</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Walking through the museum, the ancient sculptures fascinated Maria.</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Walking through the museum</t>
-        </is>
-      </c>
+          <t>A city library tracked how many patrons checked out books in two neighborhoods over a six-week period. In Neighborhood A, weekly checkouts were 120, 130, 125, 140, 150, and 145. In Neighborhood B, weekly checkouts were 90, 95, 100, 85, 80, and 75. The library also recorded the total checkouts across both neighborhoods each week: 210, 225, 225, 225, 230, and 220.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Based on the data, which statement is best supported about the change in weekly checkouts from Week 1 to Week 6?</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Walking through the museum, Maria was fascinated by the ancient sculptures.</t>
+          <t>Neighborhood A’s weekly checkouts increased by 25 from Week 1 to Week 6, while Neighborhood B’s weekly checkouts decreased by 15.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Walking through the museum, the ancient sculptures fascinated Maria.</t>
+          <t>The total weekly checkouts increased by 10 from Week 1 to Week 6.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Maria, walking through the museum, fascinated the ancient sculptures.</t>
+          <t>Neighborhood A’s average weekly checkouts were higher than Neighborhood B’s average weekly checkouts by 15.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Walking through the museum, fascinated by the ancient sculptures was Maria.</t>
+          <t>Neighborhood B’s weekly checkouts increased overall from Week 1 to Week 6.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2336,69 +2295,61 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Option A correctly places the modifier 'Walking through the museum' to clearly refer to 'Maria,' the intended subject of the action. The original sentence and other options either create a dangling modifier or incorrectly apply the modifier to the wrong noun.</t>
+          <t>From Week 1 to Week 6, Neighborhood A went from 120 to 145, an increase of 25. Over the same period, Neighborhood B went from 90 to 75, a decrease of 15. Thus, option A accurately describes both changes. Option C is not correct because the average difference is not 15, and option D is false because Neighborhood B decreased overall.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>69a2971a-a971-4b77-96f3-12512a6925e7</t>
+          <t>71ceb791-8ae7-4f9b-bd56-3d89fa227646</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Standard English Conventions</t>
+          <t>Information and Ideas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Modifiers</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eager to impress the judges, the painting was completed by Maria just before the art competition deadline.</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Eager to impress the judges, the painting was completed by Maria just before the art competition deadline.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Eager to impress the judges, the painting was completed by Maria</t>
-        </is>
-      </c>
+          <t>A city tracks the monthly proportion of residents who report using public transit at least three times per week. In January, 18% reported such use. By March, the proportion rises to 24%. The city introduces a fare discount starting in April. After the start, the reported proportions are: April 22%, May 26%, June 27%, July 25%, and August 28%. The city also records changes in total ridership (in thousands of trips) over the same months: January 210, March 235, April 228, May 252, June 260, July 258, and August 270. Across the period from January to August, both measures increase overall, but the month-to-month changes do not always move in the same direction.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Which choice best clarifies the intended meaning while following standard written English?</t>
+          <t>Based on the information in the passage, which statement is best supported about the relationship between the monthly proportion of residents using public transit at least three times per week and total ridership across all listed month-to-month transitions (January→March, March→April, April→May, May→June, June→July, and July→August)?</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Eager to impress the judges, Maria completed the painting</t>
+          <t>In every listed transition, the direction of change in the proportion matches the direction of change in total ridership.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Eager to impress the judges, the painting was completed by Maria</t>
+          <t>In some listed transitions, the direction of change in the proportion matches the direction of change in total ridership, and in other listed transitions it does not.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>The painting, eager to impress the judges, was completed by Maria</t>
+          <t>Whenever the proportion increases from one listed month to the next, total ridership decreases.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>The painting was completed by Maria, eager to impress the judges</t>
+          <t>Whenever the proportion decreases from one listed month to the next, total ridership increases.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2408,14 +2359,21 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Option A correctly links the modifier 'Eager to impress the judges' to Maria, who is the one with the eagerness. The other options misplace or dangle the modifier, incorrectly suggesting the painting itself is eager.</t>
+          <t>Compare the direction of change in the proportion with the direction of change in total ridership for each listed transition:
+- January→March: 18%→24% (increase) and 210→235 (increase)
+- March→April: 24%→22% (decrease) and 235→228 (decrease)
+- April→May: 22%→26% (increase) and 228→252 (increase)
+- May→June: 26%→27% (increase) and 252→260 (increase)
+- June→July: 27%→25% (decrease) and 260→258 (decrease)
+- July→August: 25%→28% (increase) and 258→270 (increase)
+In every listed transition, the directions match. Therefore, the best supported statement is option A.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5790d328-ff28-4fde-b2f2-fd86f91bcbca</t>
+          <t>713d38a3-0ce6-4e26-941d-49e0998d64f0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2425,52 +2383,52 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Modifiers</t>
+          <t>Boundaries</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>After analyzing the ancient manuscripts for several months, the conclusions drawn by the research team were considered groundbreaking.</t>
+          <t>Because the museum opens at nine o'clock, the tour begins immediately after it finishes checking tickets.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>After analyzing the ancient manuscripts for several months, the conclusions drawn by the research team were considered groundbreaking.</t>
+          <t>Because the museum opens at nine o'clock, the tour begins immediately after it finishes checking tickets.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>After analyzing the ancient manuscripts for several months</t>
+          <t>Because the museum opens at nine o'clock,</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Which choice best clarifies the intended meaning while following standard written English?</t>
+          <t>Which choice completes the sentence so that it conforms to the conventions of Standard English?</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>After analyzing the ancient manuscripts for several months, the research team drew conclusions that were considered groundbreaking.</t>
+          <t>Because the museum opens at nine o'clock, the tour begins immediately after it finishes checking tickets.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>After analyzing the ancient manuscripts for several months, the conclusions drawn by the research team were considered groundbreaking.</t>
+          <t>Because the museum opens at nine o'clock the tour begins immediately after it finishes checking tickets.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>The research team, after analyzing the ancient manuscripts for several months, considered the conclusions drawn groundbreaking.</t>
+          <t>Because the museum opens at nine o'clock; the tour begins immediately after it finishes checking tickets.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>The conclusions drawn by the research team, after analyzing the ancient manuscripts for several months, were considered groundbreaking.</t>
+          <t>Because the museum opens at nine o'clock, the tour begins immediately after it finishes checking tickets;</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2480,14 +2438,14 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Option A correctly links the modifier to the intended subject, 'the research team,' clarifying who did the analyzing. Other options incorrectly link the modifier, leading to a dangling or misplaced modifier problem.</t>
+          <t>The dependent clause beginning with "Because" must be followed by a comma when it precedes the independent clause. Choice A correctly uses a comma after "nine o'clock" and ends the sentence properly. The other choices omit the needed comma, use the wrong punctuation for this boundary, or introduce an incorrect trailing semicolon.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42988be9-a401-4bf8-909e-c77aafca2d51</t>
+          <t>729763cc-00cf-43b6-ae2c-dbe4b81917a6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2497,69 +2455,69 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Punctuation</t>
+          <t>Boundaries</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Over the summer Maya studied marine biology, she learned about ocean ecosystems and the creatures that inhabit them.</t>
+          <t>When the survey ended, the researchers reviewed the responses, and as expected, adjusted their estimates.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Over the summer Maya studied marine biology, she learned about ocean ecosystems and the creatures that inhabit them.</t>
+          <t>When the survey ended, the researchers reviewed the responses, and as expected, adjusted their estimates.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>marine biology, she</t>
+          <t>and as expected, adjusted their estimates</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Which choice correctly places punctuation to conform to Standard English?</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>marine biology. She</t>
+          <t>and, as expected, adjusted their estimates</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>marine biology; she</t>
+          <t>and as expected, adjusted their estimates</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>marine biology she</t>
+          <t>and, as expected adjusted their estimates</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>marine biology, she</t>
+          <t>and, as expected adjusted, their estimates</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>The sentence involves joining two independent clauses. Option B correctly uses a semicolon to separate the clauses, which is appropriate for connecting related independent clauses. Option A incorrectly uses a period, which is less effective at showing the relationship between the clauses. Option C lacks any punctuation, resulting in a run-on sentence. Option D incorrectly uses a comma, which is grammatically incorrect for joining two independent clauses without a conjunction.</t>
+          <t>In this sentence, “as expected” is a nonessential parenthetical phrase. Nonessential elements must be set off by commas, so commas are needed both before and after “as expected.” Option A correctly places both commas; the other choices leave out a required comma or place commas incorrectly.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>67575ecf-db02-45b0-a539-be64a8f8b22f</t>
+          <t>86561cc9-8def-4bb2-823e-44b2edac3feb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2569,69 +2527,69 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Punctuation</t>
+          <t>Boundaries</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The scientist collected several plant samples from the rainforest the most intriguing of which displayed unusual patterns of leaf growth.</t>
+          <t>Because the museum reopened in spring, the exhibit drew record attendance and visitors stayed longer than usual.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The scientist collected several plant samples from the rainforest the most intriguing of which displayed unusual patterns of leaf growth.</t>
+          <t>Because the museum reopened in spring, the exhibit drew record attendance and visitors stayed longer than usual.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>the most intriguing of which</t>
+          <t>the exhibit drew record attendance and visitors stayed longer than usual</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>Which choice correctly places punctuation to separate the two independent clauses inside the sentence? The independent clauses are "the exhibit drew record attendance" and "visitors stayed longer than usual."</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>, the most intriguing of which,</t>
+          <t>Because the museum reopened in spring, the exhibit drew record attendance and visitors stayed longer than usual.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>; the most intriguing of which</t>
+          <t>Because the museum reopened in spring, the exhibit drew record attendance; visitors stayed longer than usual.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>: the most intriguing of which</t>
+          <t>Because the museum reopened in spring, the exhibit drew record attendance and, visitors stayed longer than usual.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>the most intriguing of which</t>
+          <t>Because the museum reopened in spring, the exhibit drew record attendance, and visitors stayed longer than usual.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>The correct option A uses commas to set off the nonrestrictive clause, which is necessary to separate it from the main clause. Other options fail to correctly punctuate the sentence, leading to incorrect sentence structure.</t>
+          <t>The clauses "the exhibit drew record attendance" and "visitors stayed longer than usual" are both independent. They should be separated with a comma before the coordinating conjunction "and." Option D places that comma correctly. Option A leaves the clauses run together without the needed comma. Option B incorrectly uses a semicolon while keeping "and". Option C incorrectly inserts a comma after "and."</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>82e7819c-5dd0-4005-b140-62e8465b37ff</t>
+          <t>d2eaa7af-1e36-445d-8768-b5e1bb755507</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2641,79 +2599,79 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Punctuation</t>
+          <t>Form, Structure, and Sense</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Although Dr. Li’s research findings were initially met with skepticism[editable], subsequent peer reviews confirmed the validity of her methods and results.</t>
+          <t>The museum staff decided that the new exhibit would open in June, but they postponed announcing the exact date until later.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Although Dr. Li’s research findings were initially met with skepticism[editable], subsequent peer reviews confirmed the validity of her methods and results.</t>
+          <t>The museum staff decided that the new exhibit would open in June, but they postponed announcing the exact date until later.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>skepticism[editable]</t>
+          <t>postponed announcing</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Which choice completes the text so that it conforms to the conventions of Standard English?</t>
+          <t>The museum staff decided that the new exhibit would open in June, but they __________ the exact date until later.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>skepticism; subsequent</t>
+          <t>postponed announcing</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>skepticism. Subsequent</t>
+          <t>postponing to announce</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>skepticism, subsequent</t>
+          <t>had postponed to announce</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>skepticism subsequent</t>
+          <t>would postpone announce</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>The sentence requires a comma after 'skepticism' to correctly join the dependent clause 'Although Dr. Li’s research findings were initially met with skepticism' with the main clause 'subsequent peer reviews confirmed the validity of her methods and results.' Choices A and B incorrectly use a semicolon and a period, respectively, which are unnecessary here. Choice D lacks any punctuation, making it incorrect.</t>
+          <t>After “but,” the sentence requires a past-tense verb that matches the earlier past-tense “decided.” “Postponed announcing” forms a correct past-tense verb phrase with the gerund “announcing.” The other choices have incorrect or mismatched verb forms (for example, using an incorrect infinitive/gerund structure or wrong verb form after “would”).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a114fbd3-5f70-4d71-852b-fe43abd6d532</t>
+          <t>5089b33f-c0e3-481b-9057-d3e7d280f5a3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Transitions</t>
+          <t>Boundaries</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2723,42 +2681,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Many medicinal plants have been used for centuries to treat illnesses. However, modern scientific studies are just beginning to confirm the effectiveness of some of these traditional remedies.</t>
+          <t>The committee met on Tuesday, and it reviewed the proposals for the upcoming festival.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Many medicinal plants have been used for centuries to treat illnesses. However, modern scientific studies are just beginning to confirm the effectiveness of some of these traditional remedies.</t>
+          <t>The committee met on Tuesday, and it reviewed the proposals for the upcoming festival.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>However,</t>
+          <t>The committee met on Tuesday, and it reviewed the proposals for the upcoming festival.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Which choice best connects the ideas in the text?</t>
+          <t>Which choice correctly conforms to Standard English by separating the two independent clauses?</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>However,</t>
+          <t>The committee met on Tuesday, and it reviewed the proposals for the upcoming festival.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Therefore,</t>
+          <t>The committee met on Tuesday and it reviewed the proposals for the upcoming festival.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Similarly,</t>
+          <t>The committee met on Tuesday it reviewed the proposals for the upcoming festival.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>For instance,</t>
+          <t>The committee met on Tuesday, it reviewed the proposals for the upcoming festival.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2768,24 +2726,24 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>The passage presents a contrast between the historical use of medicinal plants and modern scientific validation. 'However,' correctly indicates this contrast.</t>
+          <t>The sentence contains two independent clauses: “The committee met on Tuesday” and “it reviewed the proposals for the upcoming festival.” To join independent clauses, Standard English can use a comma with a coordinating conjunction (FANBOYS), as in choice A. Choice B lacks the necessary comma. Choice C is missing both a comma and a conjunction. Choice D creates a comma splice by using a comma without a conjunction.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b8bbfecd-675d-4577-8b4c-0c55564f6f51</t>
+          <t>c30ba40f-2b4d-419e-8f49-b120c612b3dd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Transitions</t>
+          <t>Boundaries</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2795,42 +2753,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Many early astronomers believed that the stars were fixed points of light; however, later observations revealed that stars can vary in brightness and position over time.</t>
+          <t>Because the committee met earlier than usual, the agenda was revised before the public session began.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Many early astronomers believed that the stars were fixed points of light; however, later observations revealed that stars can vary in brightness and position over time.</t>
+          <t>Because the committee met earlier than usual, the agenda was revised before the public session began.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>however</t>
+          <t>Because the committee met earlier than usual</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Which choice best connects the ideas in the text?</t>
+          <t>Which choice completes the sentence so that it conforms to Standard English?</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>however</t>
+          <t>Because the committee met earlier than usual</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>therefore</t>
+          <t>Because the committee met earlier than usual,</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>in addition</t>
+          <t>Because, the committee met earlier than usual</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>for example</t>
+          <t>Because the committee met earlier than usual, the agenda was revised before</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2840,24 +2798,24 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>The transition 'however' correctly expresses the contrast between early beliefs about stars and later observations. The other options do not logically connect the ideas as effectively.</t>
+          <t>The comma after a dependent clause (introduced by “Because”) is correct: the correct sentence structure is “Because + dependent clause, + independent clause.” Choice B incorrectly adds an extra comma within the dependent clause, and choices C and D create punctuation/structure errors that make the sentence not conform to Standard English conventions.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>665795ee-29b7-424e-b97d-ca6f92cae8c6</t>
+          <t>d0be5098-41a4-461d-8b84-66bc1d22c1cb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Transitions</t>
+          <t>Boundaries</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2867,69 +2825,69 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Many early astronomers believed that all celestial bodies revolved around the Earth; [Transition] later discoveries demonstrated that the planets orbit the sun instead.</t>
+          <t>Because the committee had not yet received the audit results, the board delayed the report until next month, and then it adjusted its schedule.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Many early astronomers believed that all celestial bodies revolved around the Earth; [Transition] later discoveries demonstrated that the planets orbit the sun instead.</t>
+          <t>Because the committee had not yet received the audit results, the board delayed the report until next month, and then it adjusted its schedule.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[Transition]</t>
+          <t>the board delayed the report until next month</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Which choice best connects the ideas in the text?</t>
+          <t>Which choice most effectively completes the sentence so that it conforms to Standard English?</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>however,</t>
+          <t>the board delayed the report until next month</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>similarly,</t>
+          <t>the board delayed the report, until next month</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>subsequently,</t>
+          <t>the board delayed the report until next month and then it adjusted its schedule</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>for example,</t>
+          <t>the board delayed the report until next month; and it adjusted its schedule</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>The passage contrasts earlier beliefs with later discoveries, indicating a chronological progression. 'Subsequently,' accurately conveys this temporal relationship.</t>
+          <t>The sentence has an introductory dependent clause (“Because the committee had not yet received the audit results”) followed by the main clause. The main clause should read smoothly without interrupting the verb phrase with a comma. Because the delay happens as a single action described by “delayed … until next month,” option B wrongly inserts a comma inside the verb phrase. Options C and D change the structure by adding additional clause material into the editable portion, which is not the intended boundary placement tested here.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bafc6d2b-3ce8-431f-ab62-ed78f4f0583f</t>
+          <t>379d279a-7d38-4ec8-9fbb-72965c5e2a3b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Form, Structure, and Sense</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2939,69 +2897,69 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Many birds migrate thousands of miles each year. These long journeys help birds find food and safe nesting sites. For example, Arctic terns travel from the Arctic to the Antarctic and back again every year. (To illustrate one species’ journey, insert this sentence after the second sentence.)</t>
+          <t>Although the museum closes at 5 p.m., the gift shop ____ until 6 p.m.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Many birds migrate thousands of miles each year. These long journeys help birds find food and safe nesting sites. For example, Arctic terns travel from the Arctic to the Antarctic and back again every year. (To illustrate one species’ journey, insert this sentence after the second sentence.)</t>
+          <t>Although the museum closes at 5 p.m., the gift shop ____ until 6 p.m.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>For example, Arctic terns travel from the Arctic to the Antarctic and back again every year.</t>
+          <t>____</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Where should the sentence 'For example, Arctic terns travel from the Arctic to the Antarctic and back again every year.' be placed to best improve the organization of the passage?</t>
+          <t>Which choice completes the sentence so that it conforms to Standard English?</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>After the first sentence.</t>
+          <t>stays open</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>After the second sentence.</t>
+          <t>stay open</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>After the third sentence.</t>
+          <t>stays opened</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Before the first sentence.</t>
+          <t>staying open</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Placing the sentence after the second sentence provides a specific example that illustrates the general statement about birds undertaking long journeys to find food and safe nesting sites, thereby improving the logical flow and coherence of the passage.</t>
+          <t>The subject of the second clause is singular, “the gift shop,” so the main verb must be singular present tense: “stays.” Here, “open” is a predicate adjective that follows “stays” (“stays open”). “Stay open” does not agree with the singular subject. “Stays opened” is incorrect because “opened” is the wrong participle form. “Staying open” is non-finite and cannot serve as the main verb in this clause.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08901dcc-f5fd-43b2-adb1-8a8efffeb975</t>
+          <t>8ed754d1-1f41-4b03-b48a-82c0afd913a7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Form, Structure, and Sense</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3011,69 +2969,69 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magnetic resonance imaging (MRI) is a noninvasive technique that uses magnetic fields and radio waves to produce detailed images of the body's internal structures. Because MRI does not involve ionizing radiation, it is often preferred over other imaging methods such as X-rays or CT scans. As a result, MRI has become an essential tool for diagnosing a wide variety of medical conditions.</t>
+          <t>After the researchers analyzed the survey results, they found that the patterns had remained consistent across all age groups.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Magnetic resonance imaging (MRI) is a noninvasive technique that uses magnetic fields and radio waves to produce detailed images of the body's internal structures. Because MRI does not involve ionizing radiation, it is often preferred over other imaging methods such as X-rays or CT scans. As a result, MRI has become an essential tool for diagnosing a wide variety of medical conditions.</t>
+          <t>After the researchers analyzed the survey results, they found that the patterns had remained consistent across all age groups.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Because MRI does not involve ionizing radiation, it is often preferred over other imaging methods such as X-rays or CT scans.</t>
+          <t>had remained consistent</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Which choice most logically completes the text?</t>
+          <t>Which choice completes the sentence so that it conforms to Standard English?</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Because MRI does not involve ionizing radiation, it is often preferred over other imaging methods such as X-rays or CT scans.</t>
+          <t>remained consistent</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>MRI is often preferred over other imaging methods such as X-rays or CT scans because it does not involve ionizing radiation.</t>
+          <t>remains consistent</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>MRI, preferred over other imaging methods such as X-rays or CT scans, does not involve ionizing radiation.</t>
+          <t>had remained consistent</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MRI does not involve ionizing radiation, and it is often preferred over other imaging methods such as X-rays or CT scans.</t>
+          <t>was remaining consistent</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Option A most logically completes the text by maintaining the cause-effect relationship established in the passage, where MRI's lack of ionizing radiation is the reason for its preference. The other options do not maintain the coherence or logical progression as effectively.</t>
+          <t>The main verb is past tense: "found." The clause introduced by "that" describes a state that continued up to that past point. Using past perfect, "had remained," correctly signals continuity leading to "found." "Remained" is present with the past point but lacks that continuity emphasis; "remains" shifts to present tense; and "was remaining" is an incorrect progressive choice for a completed, stable condition.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ccacff95-3604-4334-99a4-489cc90a08c4</t>
+          <t>77b71957-0ca5-4d16-9fcd-9e2e4e4f5104</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Form, Structure, and Sense</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3083,69 +3041,69 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>The process of photosynthesis enables plants to convert sunlight into chemical energy. This transformation occurs in the chloroplasts—specialized organelles found in plant cells. In addition, the atmospheric oxygen essential for most life on Earth is a byproduct of this process. (To best maintain logical progression, where should the third sentence be placed?)</t>
+          <t>Because the committee has delayed its vote, the proposal [require] a revised timeline before it can be considered.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The process of photosynthesis enables plants to convert sunlight into chemical energy. This transformation occurs in the chloroplasts—specialized organelles found in plant cells. In addition, the atmospheric oxygen essential for most life on Earth is a byproduct of this process. (To best maintain logical progression, where should the third sentence be placed?)</t>
+          <t>Because the committee has delayed its vote, the proposal [require] a revised timeline before it can be considered.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>the placement of the third sentence</t>
+          <t>require</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>To best maintain logical progression, where should the third sentence be placed?</t>
+          <t>Which choice completes the sentence so that it conforms to Standard English?</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Before the first sentence.</t>
+          <t>requires</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>After the first sentence.</t>
+          <t>require</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>After the second sentence.</t>
+          <t>required</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Leave it where it is.</t>
+          <t>requiring</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Placing the third sentence after the first clarifies the importance of photosynthesis before detailing where it occurs, enhancing logical progression.</t>
+          <t>The subject of the sentence is "the proposal," which is singular. Therefore, the verb must be in the singular present tense: "requires." The base form "require" is plural (or used with a different structure), and "required" and "requiring" do not match the sentence’s required verb position.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>92649f81-bef4-4493-a2dd-a3ee5042f2ed</t>
+          <t>be4f7432-001d-4c96-bc8c-05afab1b9858</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Concision and Precision</t>
+          <t>Modifiers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3155,42 +3113,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Because of the fact that the experiment did not produce the expected results, the researchers decided to repeat their tests.</t>
+          <t>After the storm, the hikers found the map in the backpack that was missing from their group.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Because of the fact that the experiment did not produce the expected results, the researchers decided to repeat their tests.</t>
+          <t>After the storm, the hikers found the map in the backpack that was missing from their group.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Because of the fact that</t>
+          <t>in the backpack that was missing from their group</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Which choice is the clearest and most concise?</t>
+          <t>Which choice completes the sentence so that the modifier placement is correct?</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Because</t>
+          <t>in the backpack that was missing from their group</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Due to the fact that</t>
+          <t>in the missing backpack from their group</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>In light of the fact that</t>
+          <t>in the backpack missing from their group that was</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Considering that</t>
+          <t>in the backpack that was missing from their group that was</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3200,24 +3158,24 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Option A, 'Because,' is the clearest and most concise way to express the causal relationship in the sentence, avoiding unnecessary wordiness present in the other options.</t>
+          <t>Choice A correctly uses a restrictive relative clause (“that was missing from their group”) to modify “backpack,” so it is clear which item was missing. Choice B has an awkward, ungrammatical modifier attachment (“missing backpack from their group”). Choice C scrambles the structure and leaves an incomplete/incorrect construction. Choice D repeats “that was,” creating an incorrect, ungrammatical sentence.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>e10c9545-0155-498d-9a21-06722be9690c</t>
+          <t>becad836-46a3-4d00-834b-be9362612f3d</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Concision and Precision</t>
+          <t>Modifiers</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3227,69 +3185,69 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>During the Renaissance, artists such as Leonardo da Vinci, who was a painter, sculptor, and inventor, contributed in a significant manner to the advancement and progress of both scientific and artistic fields.</t>
+          <t>The committee approved the proposal after reviewing the budget that contained errors.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>During the Renaissance, artists such as Leonardo da Vinci, who was a painter, sculptor, and inventor, contributed in a significant manner to the advancement and progress of both scientific and artistic fields.</t>
+          <t>The committee approved the proposal after reviewing the budget that contained errors.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>contributed in a significant manner to the advancement and progress of both scientific and artistic fields</t>
+          <t>that contained errors</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Which choice is the clearest and most concise?</t>
+          <t>Which choice most effectively revises the sentence to conform to Standard English modifier placement?</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>significantly advanced both scientific and artistic fields</t>
+          <t>The committee approved the proposal after reviewing the budget that contained errors.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>contributed in a significant manner to the advancement and progress of both scientific and artistic fields</t>
+          <t>The committee approved the proposal after reviewing the budget, which contained errors.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>made significant contributions to the progress of scientific and artistic fields</t>
+          <t>The committee approved the proposal that contained errors after reviewing the budget.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>helped advance and progress the fields of science and art significantly</t>
+          <t>The committee approved the proposal after reviewing, the budget that contained errors.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Option A is the most concise and precise, conveying the idea effectively without unnecessary wordiness. Other options contain redundant or less precise phrasing.</t>
+          <t>The relative clause “which contained errors” should modify “the budget.” In choice B, the clause is clearly attached to “the budget” because it immediately follows that noun and is introduced by “which.” Choice A is less effective because the relative clause is not clearly marked, making the attachment to “the budget” less precise. Choice C incorrectly attaches the clause to “the proposal.” Choice D wrongly interrupts the verb phrase with a comma, disrupting modifier placement.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>931a44f5-6b96-47c5-a727-8ffdbc1d2df8</t>
+          <t>745cd9ab-c731-40b1-b83d-98a070cbcef3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Concision and Precision</t>
+          <t>Modifiers</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3299,69 +3257,69 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>In her analysis of the poem, Dr. Singh argues that the recurring imagery of water functions as a metaphor that represents and stands for the constant change in the protagonist's emotional state.</t>
+          <t>The committee will review the proposals by April 1 submitted during its meeting.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>In her analysis of the poem, Dr. Singh argues that the recurring imagery of water functions as a metaphor that represents and stands for the constant change in the protagonist's emotional state.</t>
+          <t>The committee will review the proposals by April 1 submitted during its meeting.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>functions as a metaphor that represents and stands for</t>
+          <t>by April 1 submitted during its meeting</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Which choice is the clearest and most concise?</t>
+          <t>Which choice most effectively clarifies where the phrase by April 1 modifies in the sentence by correctly positioning the information about the deadline?</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>serves as a metaphor for</t>
+          <t>by April 1 submitted during its meeting</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>functions as a metaphor that represents and stands for</t>
+          <t>by April 1, submitted during its meeting</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>works as a symbolic representation of</t>
+          <t>submitted during its meeting by April 1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>acts as a metaphorical symbol depicting</t>
+          <t>submitted by April 1 during its meeting</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Option A is the most concise and precise way to express the idea without redundancy or unnecessary wordiness.</t>
+          <t>Choice C places “by April 1” after “submitted during its meeting,” making “by April 1” clearly modify the proposals (the proposals that were submitted during its meeting by April 1). Choices A and B leave a comma structure that can still be read as modifying the committee’s review timeline, and Choice D changes the meaning by attaching “during its meeting” to a different element.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>b3ba1550-1b5e-471f-8a0c-64e3d6233317</t>
+          <t>339dad6f-2ab8-46c1-9a56-3bb554ed7d83</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rhetorical Synthesis</t>
+          <t>Punctuation</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3371,42 +3329,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dr. Lin’s research compared two methods for teaching vocabulary to middle school students. To best introduce the main finding of the study, choose the most effective sentence to insert after this one.</t>
+          <t>Researchers can estimate the age of some rocks by studying the minerals they contain which can reveal important details about those rocks.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dr. Lin’s research compared two methods for teaching vocabulary to middle school students. To best introduce the main finding of the study, choose the most effective sentence to insert after this one.</t>
+          <t>Researchers can estimate the age of some rocks by studying the minerals they contain which can reveal important details about those rocks.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>To best introduce the main finding of the study, choose the most effective sentence to insert after this one.</t>
+          <t>which can reveal important details about those rocks</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>To best introduce the main finding of the study, choose the most effective sentence to insert after this one.</t>
+          <t>Which choice correctly punctuates the sentence so that it conforms to Standard English?</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>The study found that the direct instruction method led to significantly greater vocabulary retention compared to the immersive reading approach.</t>
+          <t>which can reveal important details about those rocks,</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>The research was conducted over a period of six months with a diverse group of students.</t>
+          <t>which can reveal important details about those rocks.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>The study focused on middle school students who were learning new vocabulary.</t>
+          <t>which can reveal important details about those rocks</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>The study included two different teaching methods and measured various outcomes.</t>
+          <t>which, can reveal important details about those rocks</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3416,24 +3374,24 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Option A directly states the main finding of the study, providing a clear and relevant introduction to the results. Options B, C, and D provide additional context or detail about the study but do not directly introduce the main finding.</t>
+          <t>The phrase introduced by “which” is nonessential information. Nonessential relative clauses must be set off with commas. Because the clause appears at the end of the sentence, it should be followed by a comma.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>eab28c65-a9ee-4128-abf0-05e34395306e</t>
+          <t>0a803dd9-182d-4ad2-8e89-9f8e9c720906</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Expression of Ideas</t>
+          <t>Standard English Conventions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rhetorical Synthesis</t>
+          <t>Punctuation</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3443,42 +3401,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Archaeological studies of ancient trade routes reveal not only the exchange of goods but also the spread of cultural practices across continents. [Choose the most relevant detail to illustrate this point.]</t>
+          <t>Because the committee met late, it missed the deadline; however, the final report was still submitted on time.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Archaeological studies of ancient trade routes reveal not only the exchange of goods but also the spread of cultural practices across continents. [Choose the most relevant detail to illustrate this point.]</t>
+          <t>Because the committee met late, it missed the deadline; however, the final report was still submitted on time.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[Choose the most relevant detail to illustrate this point.]</t>
+          <t>it missed the deadline; however, the final report was still submitted on time</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Which choice best illustrates the spread of cultural practices across continents in the context of ancient trade routes?</t>
+          <t>Which choice correctly punctuates the sentence?</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>The use of similar architectural styles in distant regions.</t>
+          <t>it missed the deadline; however, the final report was still submitted on time</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>The exchange of spices and textiles between traders.</t>
+          <t>it missed the deadline, however, the final report was still submitted on time</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>The development of advanced navigation techniques.</t>
+          <t>it missed the deadline; however the final report was still submitted on time</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>The establishment of trade agreements between neighboring regions.</t>
+          <t>it missed the deadline however, the final report was still submitted on time</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3488,79 +3446,2939 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Option A directly illustrates the spread of cultural practices through the adoption of similar architectural styles across different regions, which aligns with the writer's goal to show cultural exchange. Other options focus more on trade goods or practices rather than cultural spread.</t>
+          <t>The sentence has two independent clauses: "it missed the deadline" and "the final report was still submitted on time." A semicolon correctly joins them. The conjunctive adverb "however" must be followed by a comma when it is used between clauses, giving "; however, the final report was still submitted on time." Options B, C, and D misuse or omit the required semicolon and/or comma.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6668f499-cee4-4f3a-bed0-b8764079cab2</t>
+          <t>562b18a7-bdb3-4b23-bdff-7022e3fc65a5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Punctuation</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Because the committee had not received the final budget, it postponed the vote; however, it agreed to meet again next week.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Because the committee had not received the final budget, it postponed the vote; however, it agreed to meet again next week.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>it postponed the vote; however, it agreed to meet again next week</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Which choice correctly completes the sentence so that it conforms to Standard English punctuation?</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>it postponed the vote; however, it agreed to meet again next week</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>it postponed the vote however, it agreed to meet again next week</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>it postponed the vote; however it agreed to meet again next week</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>it postponed the vote; however, it agreed to meet again next week,</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>The semicolon is correct because it joins two closely related independent clauses: (1) the committee postponed the vote and (2) it agreed to meet again next week. Also, when however is used as a conjunctive adverb to introduce the second independent clause, it is typically set off with a comma: “; however, it agreed …” Option A follows both rules. Options B and C use incorrect punctuation with the independent clauses, and D incorrectly ends the sentence with an unnecessary comma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>843a1e08-ecd4-4ae7-90e0-6d6c2447e82a</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Expression of Ideas</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Transitions</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>The city installed new bike lanes to reduce traffic congestion. However, many riders still prefer driving because they think biking will be unsafe.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>The city installed new bike lanes to reduce traffic congestion. However, many riders still prefer driving because they think biking will be unsafe.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>However</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Which transition best connects the two sentences?</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>However,</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Therefore,</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>For example,</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>In addition,</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>The first sentence states the city installed bike lanes to reduce congestion, while the second sentence presents a contrasting reason many riders still drive (they believe biking is unsafe). The contrast is best signaled by “However.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>d97b5f05-37fe-4394-867f-2b0e777b7d38</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Transitions</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>The city council expanded the public library’s hours to reduce wait times; ___, attendance increased during evenings and weekends.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>The city council expanded the public library’s hours to reduce wait times; ___, attendance increased during evenings and weekends.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>___</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Choose the transition that best completes the sentence.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>as a result</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>however</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>for example</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>in addition</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>The first clause explains an action taken to reduce wait times. The second clause reports the outcome—attendance increased. The logical relationship is cause-and-effect, so the best transition is “as a result.” “However” contrasts, “for example” introduces an illustration, and “in addition” adds information without indicating the cause-effect link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>21888742-213b-4762-a728-e86ef2acea96</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Transitions</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Researchers reported that the new dataset improved predictive accuracy; ____ , errors concentrated in rural regions, and the authors recommended additional sampling efforts rather than claiming the results were fully reliable.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Researchers reported that the new dataset improved predictive accuracy; ____ , errors concentrated in rural regions, and the authors recommended additional sampling efforts rather than claiming the results were fully reliable.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>____</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Which transition best fits in the blank to accurately reflect the relationship between the reported improvement and the authors’ decision not to claim the results were fully reliable?</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>therefore</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>however</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>for example</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>in addition</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>The sentence first notes an improvement in predictive accuracy, but it then emphasizes a limitation (“rather than claiming the results were fully reliable”). The phrase “however” signals that contrast between the overall positive finding and the authors’ refusal to fully endorse reliability. “Therefore” suggests the second clause follows from the first as a direct conclusion, “in addition” suggests support rather than contrast, and “for example” would imply the second clause is merely an illustration, not a contrasting limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ba7adbe5-38d3-4db9-81ba-0b4a4bad367a</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Maya wrote her science report and collected data from three sources. She has already drafted the results and the discussion, but she did not list the sources in her notes; she should add the sources when she presents the results.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Maya wrote her science report and collected data from three sources. She has already drafted the results and the discussion, but she did not list the sources in her notes; she should add the sources when she presents the results.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>when she presents the results</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Maya is revising her science report. Which choice best completes the sentence to improve the organization of the report?</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>after the results section</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>in the introduction before the problem is described</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>in the conclusion after she summarizes her findings</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>at the end of the results section</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>The sentence indicates that Maya should add the sources specifically when she presents the results. Choice D places the sources at the end of the results section, which matches the intended moment to cite the information. Choices A, B, and C place the sources in other sections, which does not align as directly with presenting the results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7653e63e-317a-4536-a073-a7eaada710ef</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>The committee reviewed the proposals and scheduled the interviews; however, it delayed the final vote until the interviews were completed, even though it had already collected most of the supporting data, then reviewed the proposals.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>The committee reviewed the proposals and scheduled the interviews; however, it delayed the final vote until the interviews were completed, even though it had already collected most of the supporting data, then reviewed the proposals.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>then reviewed the proposals</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Which revision best improves the organization of the sentence?</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>The committee reviewed the proposals and scheduled the interviews; however, it delayed the final vote until the interviews were completed, even though it had already collected most of the supporting data, then reviewed the proposals.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>The committee reviewed the proposals and scheduled the interviews; however, it delayed the final vote until the interviews were completed, then reviewed the proposals even though it had already collected most of the supporting data.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>The committee reviewed the proposals, then scheduled the interviews; however, it delayed the final vote until the interviews were completed even though it had already collected most of the supporting data.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>The committee reviewed the proposals and scheduled the interviews; however, it delayed the final vote until the interviews were completed, even though it had already collected most of the supporting data, and it reviewed the proposals again.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Option C is the only choice that fixes the organization problem by removing the misplaced “then reviewed the proposals” at the end and placing the action in a logical sequence: the committee reviewed the proposals, then scheduled the interviews, and finally delayed the final vote until after the interviews. Option B keeps the awkward end emphasis by making “reviewed the proposals” come after the delay, disrupting the chronology. Option A leaves the misplaced ending clause unchanged. Option D adds a new, illogical repetition (“again”) that does not correct the sequencing and introduces an unnecessary action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6e87a69c-c010-4cfd-90f5-faa4d8e83d49</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Although the report describes the committee’s findings, it also notes several limitations. To keep the main argument moving, the authors therefore place those limitations in the appendix rather than ___, where readers might be pulled away from the findings.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Although the report describes the committee’s findings, it also notes several limitations. To keep the main argument moving, the authors therefore place those limitations in the appendix rather than ___, where readers might be pulled away from the findings.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>___</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Which choice best completes the sentence to improve the organization and flow of the writer’s explanation?</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>in the main body of the report</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>in the appendix</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>in the introduction</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>among the committee members listed in the report</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>The sentence’s organization relies on a clear placement contrast: the limitations are moved to the appendix “rather than” the space where they would distract readers from the findings. The only choice that matches that alternative to the appendix is “in the main body of the report.” The other options (introduction or committee member list) are not the main argument area and would be less directly tied to the findings the authors want readers to follow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2a474f69-206a-4666-b816-45fb167e1325</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Concision and Precision</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>The committee decided to postpone the vote until next month because they needed more time to review the proposals.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>The committee decided to postpone the vote until next month because they needed more time to review the proposals.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>because they needed more time to review the proposals</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Which revision of the editable portion best improves concision and precision while keeping the meaning of the original sentence?</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>because they needed extra time to review the proposals</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>because they needed more time to review proposals</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>because they needed time to review the proposals</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>because they required time to review the proposals</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Option C best improves concision and precision by removing the unnecessary word "more" without changing the meaning. It keeps the specific subject to be reviewed, "the proposals." Option A is wordier because "extra" adds an unnecessary modifier. Option B is less precise because it drops "the," changing the specificity of what was to be reviewed. Option D keeps precision but is not as concise because "required" is lengthier than "needed."</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>f241fd30-3a4b-42bb-bd34-cdd24c75c95f</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Concision and Precision</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>In the report, the authors state that they believe the current policy is ineffective and they recommend that it be revised.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>In the report, the authors state that they believe the current policy is ineffective and they recommend that it be revised.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>they believe the current policy is ineffective and they recommend that it be revised</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Which revision most effectively improves the sentence by eliminating unnecessary wording while preserving meaning?</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>In the report, the authors state that the current policy is ineffective and recommend revising it.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>In the report, the authors state that they believe the current policy is ineffective and they recommend revising it.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>In the report, the authors state that the current policy is ineffective; therefore, they recommend revising it.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>In the report, the authors state that the current policy is ineffective and they recommend that it be revised.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Option A is the most concise revision. It preserves the authors’ meaning while removing unnecessary wording (it eliminates “they believe” and “that it be,” replacing “recommend that it be revised” with the more direct “recommend revising it”). Option B keeps extra wording (“they believe”), Option C adds an incorrect cause-and-effect connection (“therefore”), and Option D does not reduce the key unnecessary phrasing as effectively as A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0962360f-7c42-4f08-9297-4aecf41ef1dc</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Concision and Precision</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>The committee decided to postpone the vote because they were not ready to finalize the report by the deadline.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>The committee decided to postpone the vote because they were not ready to finalize the report by the deadline.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>because they were not ready to finalize the report by the deadline</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Which revision of the underlined portion most effectively improves concision and precision?</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>because they were not ready to finalize the report by the deadline</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>because they needed more time to finalize the report</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>because they were not prepared to finish the report by the deadline</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>because they were not ready to finalize the report by the scheduled deadline</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Option A is the most concise and precise because it keeps the original meaning while using the fewest necessary words. Option B is less precise because it generalizes the reason (“needed more time”) without specifying the deadline. Option C is wordy (“prepared to finish”) and slightly shifts the phrasing. Option D adds an unnecessary detail (“scheduled”) that does not improve precision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2de9072e-4d7e-429d-a039-ec702891724f</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Rhetorical Synthesis</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>When planning a school recycling program, students should first measure how much trash the school produces each week, because this baseline data helps them set achievable targets for reducing waste.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>When planning a school recycling program, students should first measure how much trash the school produces each week, because this baseline data helps them set achievable targets for reducing waste.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>because this baseline data helps them set achievable targets for reducing waste</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Which choice most effectively synthesizes the sentence’s reasoning by clarifying why students should measure the school’s weekly trash output first?</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>because this baseline data helps them set achievable targets for reducing waste</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>because this information shows whether students are personally motivated to recycle</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>because tracking the output weekly will make the program run more efficiently with fewer resources</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>because the measurement helps students set goals for classroom rewards rather than waste reduction</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>The sentence’s purpose is to justify measuring weekly trash output as a starting step so students can set realistic, achievable waste-reduction targets. Choice A directly states that measuring provides baseline data for choosing those targets. Choices B, C, and D shift the rationale to unrelated goals (motivation, efficiency/resource use, or rewards), so they do not best synthesize the specific decision-making reason in the sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>9ea24e10-26aa-413d-af75-0394c87eba55</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Rhetorical Synthesis</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>When describing a local recycling program, the report should begin by clearly stating its purpose and then explaining how residents can participate.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>When describing a local recycling program, the report should begin by clearly stating its purpose and then explaining how residents can participate.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>begin by clearly stating its purpose</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Which choice best completes the sentence to achieve the writing goal described?</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>begin by clearly stating its purpose and then explaining how residents can participate</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>begin with a brief history of recycling in the region and then summarize the program’s budget</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>begin by listing the materials collected and then describing the program’s environmental impact</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>begin by quoting a local official and then comparing similar programs in other cities</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>The goal is to set up a local recycling program by first stating its purpose and then explaining participation steps. Option A matches that exact rhetorical sequence and focus, while the others shift to unrelated or less relevant details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1194b008-b613-40ea-bcee-dbeb351b238d</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Expression of Ideas</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Rhetorical Synthesis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Recent archaeological discoveries at the coastal settlement provide evidence of early maritime trade, suggesting that the community engaged in extensive exchange networks with neighboring regions; however, the precise nature and scale of these interactions remain the subject of ongoing research.</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Recent archaeological discoveries at the coastal settlement provide evidence of early maritime trade, suggesting that the community engaged in extensive exchange networks with neighboring regions; however, the precise nature and scale of these interactions remain the subject of ongoing research.</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Recent archaeological discoveries at the coastal settlement provide evidence of early maritime trade, suggesting that the community engaged in extensive exchange networks with neighboring regions; however, the precise nature and scale of these interactions remain the subject of ongoing research.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Which choice most effectively emphasizes the uncertainty about the interactions between the coastal settlement and neighboring regions?</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Recent archaeological discoveries at the coastal settlement provide evidence of early maritime trade, suggesting that the community engaged in extensive exchange networks with neighboring regions; however, the precise nature and scale of these interactions remain the subject of ongoing research.</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Recent archaeological discoveries at the coastal settlement provide evidence of early maritime trade, suggesting that the community engaged in extensive exchange networks with neighboring regions; therefore, the precise nature and scale of these interactions are well understood.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Recent archaeological discoveries at the coastal settlement provide evidence of early maritime trade, suggesting that the community engaged in extensive exchange networks with neighboring regions; moreover, the precise nature and scale of these interactions are clearly defined.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Recent archaeological discoveries at the coastal settlement provide evidence of early maritime trade, suggesting that the community engaged in extensive exchange networks with neighboring regions; in conclusion, the precise nature and scale of these interactions are fully documented.</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Researchers compared two approaches to reducing noise in public transit stations: active noise cancellation and improved sound-dampening materials; however, because the first method requires power and specialized maintenance, the report concludes that the second method is more practical for long-term use.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Researchers compared two approaches to reducing noise in public transit stations: active noise cancellation and improved sound-dampening materials; however, because the first method requires power and specialized maintenance, the report concludes that the second method is more practical for long-term use.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>however, because the first method requires power and specialized maintenance, the report concludes that the second method is more practical for long-term use</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Which revision best preserves the original contrast-and-conclusion relationship by keeping the stated reason for the recommendation?</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>however, because the first method requires power and specialized maintenance, the report concludes that the second method is more practical for long-term use</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>however, the report concludes that the second method is more practical for long-term use because researchers found it to be cheaper to implement</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>however, the report concludes that the second method is more practical for long-term use even though the first method works well in the short term</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>however, the report concludes that the second method is more practical for long-term use because the first method can be installed without specialized maintenance</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Option A effectively emphasizes the ongoing research and uncertainty about the interactions, clearly highlighting the current lack of full understanding. The other options incorrectly suggest certainty or conclusion, which does not align with the passage's focus on ongoing investigation.</t>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Choice A best preserves the original synthesis because it keeps both parts of the contrast-and-conclusion logic: a contrast introduced by “however” followed by the specific reason the report gives for recommending the second method (“the first method requires power and specialized maintenance”). Choices B and C replace that stated reason with different justifications, and D contradicts the original claim about the first method’s specialized maintenance, weakening the intended support for the contrast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>744da5f7-601f-4f54-99b2-2bd82b12922f</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Boundaries</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>When the experiment began, the students recorded their observations, and they compared the results at the end of the day. Afterward, they submitted the report.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>When the experiment began, the students recorded their observations, and they compared the results at the end of the day. Afterward, they submitted the report.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>and they compared the results at the end of the day</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Which choice correctly completes the sentence so that it conforms to the conventions of Standard English?</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>and they compared the results at the end of the day</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>and they compared the results, at the end of the day</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>and they compared the results at the end of the day, and they submitted the report</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>and they compared the results at the end of the day; afterward, they submitted the report</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>In the completed sentence, the fixed part already includes a separate clause: “Afterward, they submitted the report.” The insertion should therefore be a simple continuation of the first independent clause with and, without adding extra duplicated clauses or unnecessary punctuation. Choice A correctly keeps “and” directly before the verb “they compared” and avoids an incorrect comma or redundant boundary structures. Choices B, C, and D introduce inappropriate punctuation or duplicate content that is already present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>f2c15c0f-6c6e-4162-b558-a61991adb238</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Boundaries</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Because the data were collected in winter, the researchers compared the results with earlier measurements; however, they also noted that temperature could affect the findings.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Because the data were collected in winter, the researchers compared the results with earlier measurements; however, they also noted that temperature could affect the findings.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>however, they also noted that temperature could affect the findings</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Which choice best completes the sentence so that it conforms to the conventions of Standard English?</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>however, they also noted that temperature could affect the findings</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>however they also noted that temperature could affect the findings</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>however, they also noted, that temperature could affect the findings</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>however they also noted that temperature, could affect the findings</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>The word however is a conjunctive adverb that introduces an independent clause. When it starts such a clause, it should be followed by a comma. Choice A correctly places the comma after however; the other choices either omit it or place commas incorrectly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1515fa0a-b42c-4665-bfb7-af1c13b238bc</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Boundaries</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Because the committee reviewed the results carefully, it was able to recommend the policy changes; later, the final vote occurred that afternoon.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Because the committee reviewed the results carefully, it was able to recommend the policy changes; later, the final vote occurred that afternoon.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>it was able to recommend the policy changes; later, the final vote occurred that afternoon</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Which choice correctly completes the sentence so that it conforms to Standard English conventions?</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>it was able to recommend the policy changes, later, the final vote occurred that afternoon</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>it was able to recommend the policy changes; later, the final vote occurred that afternoon</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>it was able to recommend the policy changes later, the final vote occurred that afternoon</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>it was able to recommend the policy changes; later the final vote occurred that afternoon,</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Option B is correct because a semicolon joins two independent clauses: “it was able to recommend the policy changes” and “the final vote occurred that afternoon.” Option A incorrectly uses a comma between independent clauses (a comma splice). Option C incorrectly removes the semicolon, leaving a comma where a boundary is needed. Option D adds a comma at the end of the sentence, which is not standard punctuation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>84fdeb9b-6547-43f5-be38-aa72632683f2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Form, Structure, and Sense</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>During the experiment, the students recorded the data and ____.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>During the experiment, the students recorded the data and ____.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>compared the data to their results from last year</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Which choice completes the sentence so that it conforms to the conventions of Standard English?</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>compared the data to their results from last year</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>compared it to their results from last year</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>and compared it to their results from last year</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>and they compared it to their results from last year</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>The sentence has a coordinated structure: “recorded the data and ____.” After “and,” the blank must be a parallel verb phrase describing the students’ second action. Choice A, “compared the data to their results from last year,” forms a clean parallel construction: “recorded the data and compared the data.” Choice B changes “the data” to “it,” which does not follow the convention of using a clear, specific reference when the noun it replaces is necessary for precise meaning in the parallel structure. Choices C and D incorrectly add extra conjunction structure after “and.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>05e14355-29e0-4b52-ac91-91cf317f1d93</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Form, Structure, and Sense</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Although the committee members debated the proposal for weeks, they finally voted to approve the plan, which the chair had presented.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Although the committee members debated the proposal for weeks, they finally voted to approve the plan, which the chair had presented.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>which the chair had presented</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Which choice completes the sentence so that it conforms to Standard English?</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>that the chair had presented</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>which the chair had presented</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>that the chair presented</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>which the chair has presented</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>The comma signals a nonessential relative clause, which must use “which,” not “that.” Also, the chair presented the plan before the committee voted, so the verb in the relative clause must be past perfect: “had presented.” Only choice B uses both the correct relative pronoun and the correct tense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>7ba77145-1c7a-443c-b005-f3449df4471b</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Form, Structure, and Sense</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Although the committee had reviewed the proposals, it still needed to decide whether to approve the revised budget or to request additional information from the departments that [HAS/HAVE] not yet submitted their estimates.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Although the committee had reviewed the proposals, it still needed to decide whether to approve the revised budget or to request additional information from the departments that [HAS/HAVE] not yet submitted their estimates.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>HAS/HAVE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Which choice completes the sentence so that it conforms to the conventions of Standard English?</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>HAVE</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>HAS HAD</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>HAVE HAD</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>The subject of the clause is "the departments," which is plural. Therefore, the verb should be "have": "the departments that have not yet submitted their estimates."</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>98512507-732d-4866-9f5d-0cf18a129bf3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Modifiers</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>After the storm passed, the town received reports that were not yet verified by officials.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>After the storm passed, the town received reports that were not yet verified by officials.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>reports that were not yet verified by officials</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Which choice most effectively revises the sentence to conform to the conventions of Standard English?</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>reports that were not yet verified by officials</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>reports not yet verified by officials</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>reports by officials that were not yet verified</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>reports that were not yet verified officials</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Choice A is correct because it uses a relative clause correctly: the phrase “that were not yet verified by officials” modifies the noun “reports.” Choice B is incorrect because it omits the relative pronoun “that,” so the modifier clause does not attach properly to “reports.” Choice C is incorrect because it attaches “by officials” in a way that changes the construction; the sentence suggests the reports are identified by officials rather than that the reports themselves were not yet verified by them. Choice D is incorrect because it removes the necessary word “were” before “officials,” resulting in an ungrammatical structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1b5d9c1c-9503-483b-a408-adaf5cc53e91</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Modifiers</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>The committee approved the proposal after reviewing the budget that the treasurer submitted.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>The committee approved the proposal after reviewing the budget that the treasurer submitted.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>the budget that the treasurer submitted</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Which choice, if inserted immediately after the word "reviewing," best completes the sentence by correcting the modifier relationship? Keep the rest of the sentence exactly as written.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>the budget the treasurer submitted</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>the budget that the treasurer submitted</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>the budget submitted by treasurer</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>the budget, submitted by the treasurer</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>The phrase after "reviewing" should specify which budget the committee reviewed. Choice B correctly forms a relative clause—"that the treasurer submitted"—that clearly modifies "the budget." The other choices either omit the standard relative marker (A), use an incorrect form for the agent (C), or add unnecessary punctuation that makes the modifier attachment less standard (D).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>869f5a65-5014-47b3-86b2-1dd2bccaa761</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Standard English Conventions</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Modifiers</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>The investigator interviewed the witness after which the witness later withdrew the claim.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>The investigator interviewed the witness after which the witness later withdrew the claim.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>after which the witness later withdrew the claim</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Which choice completes the sentence so that the modifier clearly and correctly refers to the intended word?</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>after which the witness later withdrew the claim</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>after the witness later withdrew the claim</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>after which the claim was later withdrawn</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>after the report was later withdrawn</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>The intended referent is the witness. Choice A uses a relative marker (“after which”) that can refer to the immediately preceding noun (“the witness”), keeping the timing information linked to the witness. Choice B turns the modifier into an open-ended time phrase that does not clearly connect the timing to the witness. Choice C shifts the subject of the action to “the claim,” so the modifier’s referent is no longer the witness. Choice D makes an incorrect referent because “the report” is not the noun the modifier is meant to describe being withdrawn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>aa0413f0-ac81-4af7-9980-5539e984dbc1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Words in Context</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>In many museums, curators label objects in two ways: by what they are and by how they were used. A carved stone tablet, for example, might be described as “ritual,” meaning it was connected to religious practice. The label then adds a second clue—small scratches where hands would grip it. Because the description moves from broad category to specific evidence, readers can infer the word “ritual” more precisely than if it stood alone. When a label offers both a claim and supporting details, the meaning of a careful term becomes easier to grasp, not harder.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>In the passage, the word “ritual” most nearly means:</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>connected to religious practice</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>made for everyday use</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>decorated only for appearance</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>broken into small pieces</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>The passage states that “ritual” means it was “connected to religious practice,” and the surrounding details (the second clue about scratches) explain how the label supports that meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>809ba6bc-4281-40e7-b14c-8a0d6b21ace5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Words in Context</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>In 19th-century cities, municipal planners often described street lighting as “improving safety.” Yet the language of improvement concealed a different goal: reducing theft by extending visibility into the hours when people would otherwise be indoors. Researchers later compared records of burglaries with the installation dates of lamps and found that crime declined most sharply in areas where light was both steady and evenly distributed. When illumination was intermittent—shining only at certain angles—reports did not change much. Thus, the term “safety” functioned as a persuasive label, while the evidence pointed to a more specific mechanism: consistent visibility altered opportunity.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>In the passage, the word “concealed” most nearly means</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>revealed</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>forgotten</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>The passage contrasts planners’ public claim with their actual goal: the language of improvement “concealed a different goal.” That means the goal was kept from being noticed—so “hidden” is the closest meaning. “Revealed” is the opposite, and “measured” and “forgotten” do not fit the context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6dc23140-a112-4423-8aa1-c06fa94535ad</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Words in Context</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>In many coastal cities, salt marshes are treated as “natural buffers” that blunt storm surge. Yet ecologists note that this buffering is not constant. When marsh surfaces are elevated by sediment, wave energy dissipates; when erosion lowers the ground, the same tides arrive with greater force. The word “buffer” therefore obscures a conditional mechanism: marshes reduce impact only insofar as their microtopography and vegetation remain intact. Restoration plans often aim not merely to add plants, but to rebuild the processes that keep sediment accumulating. In that sense, the marsh does not passively resist water; it actively maintains the conditions under which resistance is possible.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>In the passage, the word “obscures” most nearly means</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>hides or masks</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>repeats</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>measures</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>confirms</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>The passage says that calling marshes “natural buffers” is misleading because it “obscures a conditional mechanism.” That means the term hides/masks the fact that marshes reduce storm impact only when conditions like intact microtopography and vegetation hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>731d733d-7d10-43f1-8321-4c0931ea979c</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Text Structure</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>In many schools, students are encouraged to read widely because different texts build different skills. For example, a science article teaches readers to track claims and evidence, while a historical account highlights cause and effect. However, reading broadly does not automatically improve comprehension. Instead, improvement depends on how readers respond to what they read. When students pause to ask why a detail matters or how one idea leads to the next, they practice the same thinking that writers use to organize information. Therefore, teachers often pair reading with brief prompts that guide students’ attention. In this way, the goal is not just more pages, but clearer connections between ideas.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Which choice best describes the passage’s overall structure?</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>It presents a claim about reading, gives examples of how different texts build different skills, and then explains why reading alone is insufficient before concluding with a solution teachers use.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>It argues that all texts develop the same reading skill, provides one example to support that claim, and ends by listing reasons students struggle with comprehension.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>It starts by describing a teacher’s method, then contrasts two student responses to reading, and finally concludes that reading widely is unnecessary.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>It describes two separate benefits of reading, explains each benefit with an example, and ends by suggesting that comprehension improves automatically.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>The passage begins with a general claim (reading widely builds skills), supports it with examples (science vs. history), then adds a complication (reading broadly doesn’t automatically improve comprehension). It follows with an explanation of what drives improvement (how readers respond and ask questions) and concludes by stating the solution teachers use (paired prompts to create clearer connections).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>058e7f83-e79d-403b-9591-893f4ae559bd</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Text Structure</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>In studies of coastal erosion, researchers often describe shoreline retreat as a simple response to wave energy. On this view, stronger storms produce deeper undercutting, and the rate of loss follows the intensity of impact. However, such explanations treat the coast as a passive boundary rather than a changing system. For example, when sediment supply declines, the seabed can become exposed and less able to absorb wave force, which alters not only how much material is removed but where it accumulates. Consequently, erosion may accelerate even during seasons with moderate storms. Thus, the pattern of retreat reflects interactions among energy, sediment, and timing, not energy alone.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Which choice best describes the passage’s overall structure?</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>It first presents a common explanation for shoreline retreat, then criticizes it and supports the critique with an example, and finally concludes by summarizing the alternative framework.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>It starts by defining shoreline retreat in technical terms, then outlines a method for measuring wave energy, and ends by arguing that additional measurement is needed.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>It compares two different explanations for coastal erosion, then rejects both and offers a third explanation that is unrelated to the example provided.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>It begins with a broad conclusion about what causes erosion, then gives several counterexamples, and finishes by returning to the original conclusion without any new synthesis.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>The passage opens with a “simple response” view of shoreline retreat (wave energy as the main driver). It then shifts to critique that view as treating the coast as passive, using an example about declining sediment supply and how it changes wave absorption. Finally, it synthesizes the argument by concluding that retreat depends on interactions among energy, sediment, and timing rather than energy alone. The other choices describe structures (a measurement method, rejecting multiple explanations, or returning to an unchanged conclusion) that the passage does not follow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1007e84f-18d0-4d07-86c1-d43f19728571</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Text Structure</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>For decades, historians treated the early republic’s public ceremonies as simple reflections of shared values: parades, oaths, and speeches were assumed to mirror consensus. Yet the record of these events reveals a more deliberate design. Organizers repeatedly paired civic rituals with legal language, using the cadence of statutes to make political identity feel enforceable. However, this linkage did not merely stabilize belief; it also redirected it. When disputes over eligibility surfaced, officials increased the ceremonial emphasis on procedure—who may speak, when, and under whose authority—so that disagreement could be framed as a technical error rather than a moral conflict. In this way, ceremony operated less as celebration than as governance, shaping what citizens could reasonably interpret as legitimate.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Which choice best describes the passage’s overall organizational structure?</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>It contrasts an earlier interpretation with a revised one, then explains how the revised interpretation changes the events’ meaning.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>It lists several examples of public ceremonies, then concludes with a single general definition of ceremony’s purpose.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>It presents a chronological account of how organizers’ goals evolved, ending with the most recent effect on citizens.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>It argues that historians’ views are incomplete, then provides multiple competing explanations for the same outcome before settling on one.</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>The passage begins by describing historians’ earlier view (ceremonies reflect consensus), then introduces a revised claim (events show deliberate design). It further explains the consequences of that design (shifts disputes toward technical procedure rather than moral conflict), and ends by summarizing ceremony’s governance function. This matches a contrast-and-revision structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>299d128b-6ecd-47b8-9bcb-d5c3c94c168f</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cross-Text</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Text 1: In cities, streetlights do more than help people see. When light spills into the night sky, it can confuse animals that rely on dark conditions. For example, some insects follow moonlight to find open areas, but bright lighting can pull them toward walls and outdoor lamps. As a result, fewer insects reach safe feeding places, which can affect birds that eat them.
+Text 2: A town council argued that streetlights still support public safety, so the goal should be to reduce glare rather than eliminate lighting. They installed fixtures with shields that point light downward and used timers to dim lights after midnight. These changes keep roads visible for drivers while limiting the stray glow that disrupts insects. The council’s plan suggests that adjusting how light is directed can address the ecological concerns described in Text 1 without removing benefits for people.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>How does Text 2 respond to the ecological concern raised in Text 1?</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>It argues that the best solution is to eliminate streetlights entirely to prevent insects from being drawn toward walls.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>It proposes reducing glare and directing light downward so that roads remain visible while limiting the stray glow that disrupts insects.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>It claims that streetlights do not affect insects because insects rely only on moonlight, not artificial lighting.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>It suggests that the ecological effects described in Text 1 can be prevented only by changing the timing of birds’ feeding rather than adjusting streetlight design.</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Text 1 explains that stray streetlight disrupts insects by pulling them away from safe feeding places, affecting birds. Text 2 addresses this by recommending fixtures with shields and timers to reduce glare and stray glow, preserving public safety while mitigating the insect disruption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7cc40593-8be7-4734-a93a-de6b19a89657</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Cross-Text</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Text 1: In studying how people remember, psychologists often describe memory as reconstructive. According to this view, later details can reshape an earlier event, so what is recalled is not a replay but a new account assembled from fragments. Because reconstruction involves selection and emphasis, two witnesses may describe the same incident differently while both sincerely believing their versions. In this way, memory’s reliability depends not only on what occurred but also on the cues present when recall is attempted.
+Text 2: A historian examining court records offers a related but narrower claim. Rather than treating recollection as freely rebuilt, the historian argues that institutional language can impose a template on testimony. When legal forms require particular categories—such as motive, intent, or timing—witnesses adapt their memories to fit the template. The historian does not deny reconstruction; instead, the historian specifies that reconstruction is constrained by the wording that surrounds questioning, turning memory into something like a collaboration between recollection and official script.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Which statement best describes how Text 2 relates to the claim in Text 1?</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Text 2 supports Text 1’s idea that recollection is reconstructed, but argues that legal or institutional wording constrains how that reconstruction happens.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Text 2 contradicts Text 1 by claiming that recollection is a direct replay of events rather than a reconstructed account.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Text 2 shifts the focus away from reliability and instead argues that memory is shaped primarily by emotional reactions, not by external cues.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Text 2 extends Text 1 by claiming that reconstruction happens only when multiple witnesses compare their accounts with one another.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Text 1 says memory is reconstructive and influenced by the cues present during recall. Text 2 agrees that reconstruction occurs, but specifies that institutional language and required categories shape the reconstruction by imposing a template on testimony.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>87479ff1-f97a-4800-b99b-014e5da82a15</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Craft and Structure</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Cross-Text</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Text 1: In ancient Rome, state historians often treated the past as a storehouse of usable lessons. They arranged events into cause-and-effect sequences so that later readers could infer which civic virtues produced stability and which vices invited disorder. Yet this clarity was partly rhetorical: by selecting a few decisive moments and linking them with confident language, historians could make complex social change appear to follow a single line of moral intention.
+Text 2: A modern historian, studying Roman records, argues that the same “lesson” structure can mislead. When historians foreground exemplary turning points, they compress competing motives—economic pressure, regional rivalry, and personal ambition—into a single moral narrative. Rather than denying that Romans valued virtue, the modern account suggests that the rhetoric of causation reflects what authors wished readers to notice, not what contemporaries experienced. In this view, the lesson is not the past itself but the author’s method of organizing evidence.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Which statement best describes how Text 2 modifies Text 1’s claim that the apparent cause-and-effect “clarity” was partly rhetorical?</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Text 2 modifies Text 1 by arguing that foregrounding turning points makes the cause-and-effect “clarity” partly rhetorical because it compresses competing motives into a single moral narrative and frames causation as reflecting what authors wished readers to notice, rather than what contemporaries experienced.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Text 2 modifies Text 1 by claiming that Roman historians rejected cause-and-effect reasoning and replaced it with explanations that ignore motives entirely.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Text 2 modifies Text 1 by arguing that the “clarity” is partly rhetorical mainly because historians used cause-and-effect sequences to reduce bias in their accounts of Roman politics.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Text 2 modifies Text 1 by asserting that compressing competing motives into a moral narrative always produces an accurate account of how social change occurred.</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Text 1 says the apparent clarity is “partly rhetorical” because historians select decisive moments and use confident language to make change seem to follow a single moral line. Text 2 specifies how this rhetorical clarity works: when historians foreground turning points, they compress competing motives into one moral narrative, and the rhetoric of causation reflects what authors wanted readers to notice rather than what contemporaries experienced. Option A matches both the mechanism (foregrounding turning points that compress motives) and the reframing of causation (author intent vs contemporaries’ experience), making it the best description of Text 2’s modification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ae1143c0-c4a3-4ffd-bc13-b3eacd0c7b48</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Central Idea</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>In the early 1800s, many cities built new water systems to reduce illness. Engineers designed pipes to bring cleaner water from farther away and to keep it separate from waste. At the same time, some neighborhoods added regular street cleaning and improved drainage so rainwater would not mix with sewage. After these changes, public health officials reported fewer outbreaks in areas that received both improved water supply and better removal of waste. The results suggested that protecting drinking water required more than one action, because contamination could still spread through the streets and drains.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Which choice best states the central idea of the passage?</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Improving public health in early 1800s cities required coordinated changes to both water supply and waste removal systems.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Street cleaning and drainage improvements were more effective than new water pipes at reducing illness outbreaks.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Engineers focused mainly on bringing clean water from farther away, while waste removal was largely handled by chance.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Public health officials concluded that fewer outbreaks occurred only when cities adopted a single, comprehensive water system.</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>The passage explains that cities reduced illness by taking multiple actions—building pipes to deliver cleaner water and separating it from waste, and also improving street cleaning and drainage to prevent mixing rainwater with sewage. It concludes that protecting drinking water required more than one action. Options B, C, and D contradict these points or introduce unsupported claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>92320f13-067b-4a3a-98a6-235415469c25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Central Idea</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>In the early twentieth century, public health officials increasingly used standardized measurements to compare outbreaks across cities. Before these practices, reports often varied in what counted as a case and how quickly observations were recorded. After adoption of common definitions and reporting schedules, researchers were able to examine whether changes in mortality followed similar patterns even when cities differed in population size. For example, when officials tracked deaths alongside the date of first reported symptoms, they found that delays in recognizing cases tended to shorten the observed period of transmission. The findings suggested that improving measurement and timing did not merely make statistics more accurate; it also affected how outbreaks appeared in the data.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Which statement best expresses the central idea of the passage?</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Standardized measurements and reporting schedules helped researchers compare outbreaks across cities and showed that better measurement could change how outbreaks appeared in the data.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Differences in population size were the main reason researchers could not previously detect similarities in outbreak patterns across cities.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Tracking deaths and the date of first reported symptoms proved that delays in recognizing cases always lengthened the period of transmission.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Before standardized case definitions were adopted, public health officials recorded observations too slowly to produce any useful mortality statistics.</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>The passage explains that adopting common case definitions and reporting schedules enabled cross-city comparisons and that improved measurement and timing affected what patterns appeared in the data. The other choices either contradict the described findings (B and C) or overstate the earlier situation (D).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>74666fdd-00a4-4b1a-bc40-221f5db6c15d</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Central Idea</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>In many colonial cities, merchants recorded transactions in ledgers that listed not only goods but also the “place of making” and the “date of arrival.” A historian comparing these records with port schedules finds that items labeled with nearby production dates often arrived weeks later than promised, while some goods marked with distant origins arrived sooner than expected. The pattern is consistent across multiple decades: delays cluster around periods when shipping capacity declined, regardless of claimed origin, and early arrivals increase when port traffic was lower. The merchant labels therefore function less as precise accounts of manufacture and more as tools for organizing credit risk and customer expectations. By linking ledger wording to shipping constraints, the historian argues that the ledgers’ central purpose was financial management under uncertainty, not logistical accuracy.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Which statement best expresses the central purpose of the merchant ledgers, according to the historian?</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>They were intended to provide logistics-accurate records of where and when goods were made and arrived.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>They were used primarily to manage financial risk and shape customer expectations despite uncertainty in shipping.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>They served mainly as shipping schedules that merchants relied on to plan departures and arrivals.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>They documented delays only for goods with nearby production dates to improve future inventory planning.</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>The passage argues that comparisons with port schedules show ledger dates do not reliably match actual arrival times. Instead, the consistent relationship between delays/early arrivals and shipping capacity suggests the labels function mainly to organize credit risk and customer expectations. Options A, C, and D contradict this synthesis or attribute narrower purposes not supported by the overall pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3b9bb8cd-bb1f-4f9e-b01d-bf05a184f720</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Command of Evidence</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>In 1890, a city council debated whether to replace its street lamps with electric lights. A report from the city engineer stated that electric lights were brighter than gas lamps and that they could be turned on and off quickly. Another document, written by a lamp repair shop, warned that early electric bulbs often burned out sooner than expected. A newspaper editorial argued that electric lights would reduce crime because the streets would be easier to see at night. The council concluded that the strongest reason to test electric lamps was their brightness and controllability, not the repair shop’s concerns or the editorial’s claim about crime.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Which statement best supports the council’s conclusion that the strongest reason to test electric lamps was their brightness and controllability?</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>The city engineer reported that electric lights were brighter than gas lamps and could be turned on and off quickly.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>The lamp repair shop warned that early electric bulbs often burned out sooner than expected.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>The newspaper editorial claimed that electric lights would reduce crime because streets would be easier to see at night.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>The council concluded that the editorial’s claim about crime was not the strongest reason to test electric lamps.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>The council’s conclusion points specifically to brightness and controllability. The city engineer’s report is the only option that directly provides both of those characteristics as evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2ff565ff-2aa6-4fdc-bc38-d5f6589d3878</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Command of Evidence</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>In 1848, a city council proposed a new street lighting plan to reduce night theft. The plan estimated that installing gas lamps at every third lamppost would cut theft by about one fifth, based on a comparison of two neighborhoods. The report also noted that the neighborhoods differed in population density and police patrol hours. A later audit counted theft incidents during the first month after installation and reported a 12% drop in the council’s district. The audit did not separate theft changes by street or compare patrol hours before and after. The council cited both the initial estimate and the audit as evidence that the lighting plan caused the reduction.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Which part of the passage provides the strongest support for the council’s claim that the lighting plan caused the reduction in theft by showing that theft decreased after the plan was implemented?</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>“The plan estimated that installing gas lamps at every third lamppost would cut theft by about one fifth, based on a comparison of two neighborhoods.”</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>“However, the report also noted that the neighborhoods differed in population density and police patrol hours.”</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>“A later audit counted theft incidents during the first month after installation and reported a 12% drop in the council’s district.”</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>“The audit did not separate theft changes by street or compare patrol hours before and after.”</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>The council’s claim depends on theft decreasing after the lighting plan was implemented. Option C directly describes a post-installation audit that reported a 12% drop in theft during the first month. Option A is only an estimate based on a comparison of neighborhoods, and Options B and D focus on differences or limitations rather than showing that theft decreased after installation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0e9ebb11-a639-4faf-a45f-1bf52f569570</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Command of Evidence</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>In 1930, a historian summarized early urban sanitation reforms by arguing that “city administrations improved public health only after they could measure sanitation outcomes.” To test this claim, archivists compared three cities’ records from 1910 to 1935. City A installed water-quality sampling in 1921 and began reporting bacterial counts annually; after 1926, the city’s typhoid rate fell steadily. City B kept detailed incident logs from 1910 onward but did not adopt standardized sampling until 1930; its typhoid rate showed irregular changes before 1930 and declined after 1930. City C adopted sampling in 1914 and reported counts, yet its typhoid rate declined mainly in two years following a major flood-control project in 1924. The historian’s conclusion depends on whether measurement preceded improvements across all three cities.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Which piece of evidence from the passage most directly supports the historian’s claim that city administrations improved public health only after they could measure sanitation outcomes?</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>City A installed water-quality sampling in 1921 and began reporting bacterial counts annually; after 1926, its typhoid rate fell steadily.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>City B kept detailed incident logs from 1910 onward but did not adopt standardized sampling until 1930; its typhoid rate declined after 1930.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>City C adopted sampling in 1914 and reported counts, yet its typhoid rate declined mainly in two years following a major flood-control project in 1924.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>The historian’s conclusion depends on whether measurement preceded improvements across all three cities.</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>The claim is specifically about improvements occurring only after measurement becomes possible. City A shows the clearest sequence: the city could measure sanitation outcomes beginning in 1921 (annual bacterial counts), and the public health improvement (steady typhoid decline) occurs after 1926. City B’s evidence is less direct because it notes irregular changes before 1930, and City C attributes the decline mainly to flood-control rather than measurement timing. Option D is meta-commentary about the historian’s dependence, not evidence supporting the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>d343c9e6-a135-493b-be5f-5eb63e8c75ee</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>In a study of city parks, researchers counted how many people visited each park during the same week. Park A had a playground and two shaded picnic areas. Park B had no playground and only open, sunny space. On three weekdays, Park A averaged 120 visitors, while Park B averaged 60. On two weekend days, Park A averaged 200 visitors, while Park B averaged 90. The researchers also noted that the weather was similar across all days and that the parks were about the same distance from the city center. From these observations, they concluded that the difference in visitor numbers was linked to features present in Park A.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Which inference is best supported by the researchers’ observations?</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Because Park A has a playground and shaded picnic areas, the researchers infer that these features are linked to Park A’s higher visitor numbers.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Because the weather and the parks’ distance were similar, the researchers infer that Park A and Park B should have had identical visitor numbers on every day.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Because Park B has only open, sunny space, the researchers infer that the fewer visitors at Park B were caused by those spaces being less appealing to visitors during the weekend.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Because Park A includes shaded areas, the researchers infer that visitors did not change their behavior from weekdays to weekends.</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>The observations show that Park A had higher average visitation than Park B on both weekdays and weekend days, and the researchers report that weather and distance were similar between the parks. This supports the conclusion that a difference in features—specifically those present in Park A—is linked to the difference in visitor numbers. 
+Option B goes beyond the evidence by claiming identical visitor numbers on every day, which the data do not show. Option C offers a specific mechanism (weekend appeal of sunny space) that is not supported by the passage. Option D incorrectly infers that visitors did not change behavior between weekdays and weekends, even though the averages increase on both parks from weekdays to weekends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>a78ade76-ff44-48cb-8016-c91a822fb0a6</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>In a study of municipal water systems, researchers compared two neighborhoods that shared similar rainfall patterns and pipe materials. Neighborhood A received water from a treatment plant that monitored chlorine levels continuously and adjusted dosage every hour. Neighborhood B relied on a daily calibration: chlorine dosage was set once each morning and not changed until the next day. Over a two-week period, Neighborhood A showed small day-to-day fluctuations in chlorine concentration and consistently low counts of bacterial growth in water samples. Neighborhood B displayed larger swings in chlorine concentration and, on several afternoons, bacterial counts rose sharply before the next morning’s adjustment. The researchers concluded that the timing of dosage changes affected bacterial growth.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Based on the researchers’ findings, which inference is most strongly supported about why Neighborhood B had more bacterial growth spikes?</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Because Neighborhood B’s chlorine dosage was adjusted only once per day, chlorine levels sometimes dropped between morning adjustments, allowing bacterial counts to rise before the next adjustment.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Because Neighborhood B received water from a different type of treatment plant than Neighborhood A, its chlorine monitoring was less accurate.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Because the neighborhoods had different rainfall patterns, Neighborhood B experienced more bacterial growth due to higher water contamination.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Because Neighborhood A’s continuous monitoring prevented any day-to-day fluctuations in chlorine concentration, which eliminated bacterial growth entirely.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>The passage links Neighborhood A’s hourly dosage adjustments and continuous monitoring to small chlorine fluctuations and low bacterial growth, while Neighborhood B’s once-daily adjustments correspond to larger chlorine swings and afternoon bacterial spikes before the next morning adjustment. The most supported inference is that in Neighborhood B chlorine levels sometimes fell between scheduled adjustments, permitting bacterial growth to rise until the next dosage change. The other options introduce differences (plant type, rainfall patterns) not stated, or overclaim (Neighborhood A had no fluctuations/bacterial growth entirely).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>23cf3f3f-f602-40cc-aabc-45f2e3b7b41d</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>In a study of coastal fish, researchers recorded oxygen levels at two depths and the fish’s vertical position each hour. At the surface, oxygen remained high and stable throughout the day. At 10 meters, oxygen declined steadily from late morning to late afternoon. The fish were most often observed near the surface during the early hours, and their presence at 10 meters decreased as the afternoon progressed. When the researchers controlled for light and temperature by selecting the same times of day across multiple days, the pattern of declining oxygen at 10 meters still coincided with the fish’s reduced time at that depth.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Based on the study, what is the most strongly supported inference about the fish’s behavior at 10 meters as the day progresses?</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>As oxygen at 10 meters declines, the fish spend less time there.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>The fish move to 10 meters later in the day to compensate for increased oxygen at the surface.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>The fish’s reduced presence at 10 meters is caused primarily by changes in light and temperature rather than oxygen.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>The fish avoid 10 meters only when oxygen at the surface becomes unstable rather than when oxygen at 10 meters declines.</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>The passage states that oxygen at 10 meters declines from late morning to late afternoon and that the fish’s time at 10 meters decreases as the afternoon progresses. It further notes that even when researchers controlled for light and temperature (using the same times across days), the oxygen decline at 10 meters still coincided with reduced time at that depth. This supports the inference that declining oxygen at 10 meters is associated with the fish spending less time there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>89be43d1-35db-4eb4-87d5-e5741543f764</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Data Interpretation</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>A school tracks how many students bring a reusable water bottle each week. In Week 1, 12 students bring bottles. In Week 2, the number rises to 15. In Week 3, it increases to 18. In Week 4, it stays at 18. Over the four weeks, the total number of students who brought bottles is 63. The school also reports that the total number of students in the grade is 30 each week.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Based on the information in the passage, what is the best interpretation of how the proportion of the 30 students in the grade who brought reusable bottles changed from Week 1 to Week 3?</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>It increased from 40% in Week 1 to 60% in Week 3.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>It increased from 30% in Week 1 to 50% in Week 3.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>It decreased from 60% in Week 1 to 40% in Week 3.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>It stayed the same at 50% from Week 1 through Week 3.</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>The grade has 30 students each week. In Week 1, the proportion is 12/30 = 40%. In Week 3, the proportion is 18/30 = 60%. Therefore, the proportion increased from 40% to 60%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86e8a76a-07c9-4ca1-9fba-370f951207c6</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Data Interpretation</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>A city tracked weekly recycling rates for two programs during the first eight weeks after launch. Program A increased from 12% in week 1 to 18% in week 4, then stayed at 18% through week 8. Program B rose from 10% in week 1 to 16% in week 3, then declined to 14% in week 4 and continued falling to 11% by week 8. In week 4, Program A recorded 18% while Program B recorded 14%. Over the full eight weeks, Program A’s average weekly recycling rate was 17%, and Program B’s average was 13%. The city reported that both programs targeted the same neighborhoods but differed in messaging frequency.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Based on the eight-week averages, what is the difference between Program A’s and Program B’s average weekly recycling rates?</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>3 percentage points</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>4 percentage points</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>5 percentage points</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>6 percentage points</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>The passage states that Program A’s average weekly recycling rate was 17% and Program B’s average was 13%. The difference is 17% − 13% = 4 percentage points, which corresponds to option B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>d42e3c6e-756c-45a0-ad90-06366374edae</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Information and Ideas</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Data Interpretation</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>A city tracked the share of commuters who used three transit options during a pilot year. In January, 40% used buses, 35% used subways, and 25% used commuter rail. By July, buses had fallen to 28%, subways had risen to 42%, and commuter rail had risen to 30%. The city also reported that the total number of commuters remained constant at 200,000 each month. No other transit modes were counted.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Based on the data, how many fewer commuters used buses in July than in January?</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>24,000</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>28,000</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Total commuters are constant at 200,000 each month. In January, 40% used buses: 0.40 × 200,000 = 80,000 commuters. In July, 28% used buses: 0.28 × 200,000 = 56,000 commuters. The difference is 80,000 − 56,000 = 24,000 fewer commuters used buses in July than in January.</t>
         </is>
       </c>
     </row>
@@ -3575,56 +6393,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>question_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>passage_valid</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>question_valid</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>difficulty_aligned</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>options_valid</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>correct_answer_valid</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>explanation_valid</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>grammar_valid</t>
         </is>
@@ -3633,7 +6451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e3494f3d-170d-4add-aa63-5f68783bb58e</t>
+          <t>5d930aa7-42ba-4fa0-9ea0-8261c83a3b6f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3641,11 +6459,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>The item passes all quality checks: the passage is clear and provides sufficient context for the target word 'invaluable'; the question is precise and tests the intended skill; the difficulty is appropriate for an easy level; the answer choices are distinct and only one is correct; the explanation is clear and accurate; and there are no grammar or clarity issues.</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>1</v>
       </c>
@@ -3671,7 +6485,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>c13acee7-0f7e-4423-ba56-f24509bdc17c</t>
+          <t>1fced7e0-f3e8-41f4-8547-446f6a8c7f38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3681,7 +6495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The item passes all quality checks: the passage is clear and provides sufficient context for the word 'novel'; the question is precise and tests the intended skill; the difficulty level is appropriate; the answer choices are distinct and only one is correct; the explanation is accurate and clear; and there are no grammar or clarity issues.</t>
+          <t>The passage provides sufficient contextual clues (“constrained interpretation,” “separating what was seen from what was inferred”) to infer that constrained means limited/restricted. The question is grammatically clear, answerable from the passage alone, and only option A is clearly correct; other options are not supported by the text. The explanation directly ties the wording to the passage’s meaning.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -3709,7 +6523,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a07f312d-751e-4d03-9467-c9566b2d991c</t>
+          <t>9e90f2fc-cc9b-4b25-b7e2-87f9bd0d5ead</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3717,11 +6531,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>The item passes all quality checks. The passage provides a clear context for the word 'ephemeral' in scientific discourse. The question is precise and aligns with the Words in Context type. The difficulty is appropriate for a hard-level SAT question, with challenging but plausible distractors. The correct answer is well-supported by the passage, and the explanation is clear and accurate.</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>1</v>
       </c>
@@ -3747,7 +6557,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e4892e3d-7bfa-4736-b3c1-3da716e25ef7</t>
+          <t>4315f9a6-5454-489e-88fa-0add269d589e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3755,11 +6565,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>The item passes all checks: the passage clearly presents a contrast in perspectives about the importance of breakfast, supporting the text structure question. The question is clear and tests the intended skill. The difficulty is appropriate for an easy level, with plausible distractors and one clearly correct answer. The explanation accurately justifies the correct answer and addresses the incorrect options. There are no grammar or clarity issues.</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>1</v>
       </c>
@@ -3785,7 +6591,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e8e44a4f-8a68-4fd3-82c6-a06a2e1e2bd4</t>
+          <t>75185ab8-59eb-4d9a-be92-a220a307c824</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3795,7 +6601,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The item passes as the passage provides a clear contrast between the role of the printing press and other factors in the Renaissance, supporting a question about text structure. The question is well-formed and aligns with the intended skill. The difficulty level is appropriate, and the answer choices are distinct and plausible, with a clear correct answer. The explanation accurately justifies the correct answer and addresses the incorrect options. There are no grammar or clarity issues.</t>
+          <t>The passage follows a clear structure: presents a common approach, then challenges it by detailing limitations, and concludes with an alternative/combined approach. Option A matches this progression best; the other options introduce elements not present in the passage (unnecessary documentary analysis, unrelated reasons, competing theories, definitive endorsement).</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -3823,7 +6629,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61b88777-6262-47e3-a6a6-829641a3580c</t>
+          <t>15b37d32-b49d-4afa-a75f-b90fa1fb81d0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3833,7 +6639,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The passage clearly contrasts traditional and contemporary views on technological innovation, supporting a Text Structure question. The question is precise and aligns with the passage's content. The difficulty is appropriate for a hard level, with plausible distractors. The correct answer is well-supported, and the explanation is clear and accurate. No grammar or clarity issues are present.</t>
+          <t>The passage follows a clear organizational pattern: describes a standard approach to interpreting ice cores, introduces a complication (diffusion) undermining key assumptions, and then offers an alternative interpretive framework (transformed message/deconvolution). Option A matches this progression. The distractors introduce incorrect elements (e.g., unnecessary dating models, comparisons of competing interpretations without basis, or avoiding diffusion rather than deconvolution) or contradict the passage’s final recommendation.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3861,7 +6667,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>686f746a-444e-412c-af99-9bbb7bfb0bca</t>
+          <t>1e2deace-4da8-445c-b9fa-ec6da6083fc2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3871,7 +6677,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The item passes all quality checks. The passage is clear and supports a cross-text comparison. The question is precise and tests the intended skill. The difficulty is appropriate for an easy level, with plausible distractors. The correct answer is supported by the passage, and the explanation is accurate and clear.</t>
+          <t>Text 2 directly addresses Text 1’s concern by reframing programs as supporting the same literacy/reading goal rather than eliminating it. Option B matches this best; the other options contradict or introduce claims not supported by the texts.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3899,7 +6705,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8aafc6c0-6ad5-47cb-a04e-b56496770eda</t>
+          <t>9be77b39-589d-42ef-86e7-5bbee8e68ae4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3907,11 +6713,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>The item passes all quality checks: the passage is clear and supports a cross-text question, the question is well-formed and tests the intended skill, the difficulty level is appropriate, the answer choices are distinct and plausible with one correct answer, and the explanation is valid and clear.</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
         <v>1</v>
       </c>
@@ -3937,7 +6739,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eb02ac38-98ec-4566-8bb6-81d2f8e716f4</t>
+          <t>26c7033c-daea-46a3-b497-949a4b8b662d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3947,7 +6749,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The item passes all validation checks. The passage is clear and provides distinct perspectives from a historian and a sociologist, supporting a cross-text analysis. The question is precise and tests the intended skill of comparing viewpoints. The difficulty level is appropriate for a hard SAT question, with challenging but plausible distractors. The correct answer is supported by the passage, and the explanation accurately justifies the correct choice while clarifying why the other options are incorrect. There are no grammar or clarity issues.</t>
+          <t>Passage clearly defines “layered” as thin coats on top of one another and uses that meaning to explain visual effects. The question directly targets the stated definition. Options are distinct, plausible, and only option A matches the passage. Explanation accurately cites the passage and aligns with the chosen meaning.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3975,7 +6777,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>d0b8ef37-0ab4-40b7-987c-0b422726bcea</t>
+          <t>f7fceb53-60ec-4d37-8a86-8e1faec93d91</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3983,11 +6785,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>The item passes as the passage clearly presents a central idea about the role of tools in human progress, which is well-aligned with the question type. The question is clear and tests the intended skill. The difficulty is appropriate, and the options are distinct with one correct answer. The explanation is accurate and comprehensive, and there are no grammar issues.</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
         <v>1</v>
       </c>
@@ -4013,7 +6811,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31acd2c0-30d8-4bb4-ae2f-a83995117484</t>
+          <t>6580bff1-3c65-4afb-b753-b3e93c51785c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4023,7 +6821,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The passage clearly presents a central idea about the impact of zoning laws on urban development. The question is well-formed and aligns with the central idea question type. The difficulty level is appropriate, with plausible distractors and a clearly correct answer. The explanation accurately justifies the correct answer and addresses the incorrect options. There are no grammar or clarity issues present.</t>
+          <t>The passage provides clear contextual clues: the text links “imprecision” to relying on sensory outcomes and “mistak[ing] correlation for mechanism.” Option B best captures that meaning (erroneous inference about causation), while the other options address measurement quality, intuition, or instrument improvement, none of which the passage attributes to “imprecision.” The explanation directly quotes and correctly derives the meaning.</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4051,7 +6849,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fd9bf197-8f2a-4e8a-9857-783fbb15b6eb</t>
+          <t>43aaf5f9-eb1c-42fd-93c5-869793ebb453</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4059,11 +6857,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>The passage clearly presents a central idea about the challenges and reform efforts in 19th-century urban centers, which is well-aligned with the question type. The question is precise and tests the intended SAT skill. The difficulty level is appropriate, with challenging distractors. The correct answer is clearly supported by the passage, and the explanation justifies the choices effectively. There are no grammatical or clarity issues present.</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>1</v>
       </c>
@@ -4089,7 +6883,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>98e258b0-4ca1-4e8b-a6f1-6bb941eca292</t>
+          <t>ed37bfa7-2a70-4118-b65b-927ba9deea11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4097,11 +6891,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>The item passes all quality checks: the passage provides a clear basis for the question, the question is well-formed and tests the intended skill, the difficulty is appropriate, the answer choices are distinct and plausible, the correct answer is well-supported, and the explanation is accurate and clear.</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
         <v>1</v>
       </c>
@@ -4127,7 +6917,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ab43c827-d23b-4108-8f11-2c47b4bce9c6</t>
+          <t>b1d3bb9e-2d0e-4db1-bc70-4188a6fd3bfe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4137,7 +6927,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The item passes all checks: the passage provides multiple plausible evidence candidates, the question is clear and tests the intended skill, the difficulty is appropriate, the options are well-constructed with one clear correct answer, and the explanation is valid and complete.</t>
+          <t>The passage’s structure is clear (initial framing → contrast with newer argument → consequences). Option A uniquely matches this progression. Other options introduce elements not present in the passage (examples of daily life, call for future research, refuting counterargument, explicit chronological trace, call for future research), making them clearly incorrect.</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -4165,7 +6955,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e18ed099-f07b-4c69-afeb-829d5101f483</t>
+          <t>72fdcfdf-52b9-47ca-9d2f-41427d8c8c03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4175,7 +6965,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The item passes all checks: the passage provides sufficient evidence for a Command of Evidence question, the question is clear and tests the intended skill, the difficulty is appropriate for a hard level, the answer choices are well-constructed with one clearly correct answer, and the explanation is accurate and complete.</t>
+          <t>Text 1 presents one argument against technology/noise in libraries; Text 2 offers a counterargument that technology-related activities extend literacy. The prompt asks for the best relationship, and option A accurately captures the contrast. Other options mischaracterize one or both texts (always included tech; return to being silent; future focus; only disagree about noise). Options are distinct and each is grammatically correct.</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -4203,7 +6993,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49914cbc-7026-49d1-a15d-e8720fe90277</t>
+          <t>9b461965-780a-470f-bc4e-ba22549c1018</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4213,7 +7003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The passage provides sufficient context about the challenges faced by rural families relying on wells during the late 1800s. The question is clear and tests the intended inference skill. The difficulty level is appropriate for an easy SAT question, and the answer choices are well-constructed with only one correct answer. The explanation correctly justifies the correct answer and why the other options are incorrect. There are no grammar or clarity issues present.</t>
+          <t>Text 2 directly revises/limits Text 1’s proxy claim by explaining that nighttime readings are informative but not sufficient, and it provides a mechanism (daytime processes) that can diverge despite similar evening temperatures. Option A captures this relationship as a challenge to proxy reliance. Other options either overstate support (B), claim identity (C), or deny relevance entirely (D).</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -4241,7 +7031,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8c23571a-fe2c-4f70-8af2-4dab6b08525b</t>
+          <t>ad124191-1ef5-44d3-ae45-987381401d6f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4249,11 +7039,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>The item passes all checks: the passage supports an inference question, the question is clear and tests the intended skill, the difficulty is appropriate, the answer choices are well-constructed with only one correct answer, and the explanation is valid and clear.</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
         <v>1</v>
       </c>
@@ -4279,7 +7065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ca57c8bf-63ed-4c01-bd5f-5f6351325bad</t>
+          <t>0c2da2af-9fc6-4b7c-9375-ff221310cdec</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4289,7 +7075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The passage provides sufficient context for an inference question, and the question is clear and precise. The difficulty level is appropriate for a hard SAT question, with plausible distractors and a clearly supported correct answer. The explanation correctly identifies why the correct answer is supported by the passage and why the other options are not. There are no grammar or clarity issues present.</t>
+          <t>The passage’s main idea is that tide charts help coastal cities make practical scheduling decisions by predicting predictable sea-level changes. Option A best captures this overall central idea, while B and C focus on single applications and D incorrectly claims tide charts are only useful when coordination is the factor preventing delays.</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -4317,7 +7103,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>b5ff952b-1c49-4cc6-8c70-097f99227959</t>
+          <t>6fe2031e-61c1-42c1-9d90-c36e98fbf104</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4327,7 +7113,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The item passes because the passage provides clear data that supports the question type. The question is well-constructed and aligns with the data interpretation skill. The difficulty level is appropriate for an easy question, with plausible distractors and a clearly correct answer. The explanation accurately justifies the correct answer and rules out the incorrect ones. There are no grammar or clarity issues.</t>
+          <t>Passage clearly contrasts earlier and later review methods for the same highway proposal, emphasizing that the later impact-assessment framework changed which information counted as relevant (secondary effects). Option A matches this central takeaway; the other options introduce claims not supported (universal rejection, greater accuracy, cost comparison).</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4355,7 +7141,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>d72e085f-817c-4265-a197-6515d3e9b2e9</t>
+          <t>ee37cc76-0481-4830-80cd-c9037f33ab09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4363,11 +7149,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>The passage provides clear data regarding public transportation usage and satisfaction, which supports the data interpretation question. The question is well-constructed, and the answer choices are plausible with one clearly correct answer. The difficulty level is appropriate, and the explanation correctly justifies the correct answer.</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
         <v>1</v>
       </c>
@@ -4393,27 +7175,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5be1e9f3-e814-43f7-a327-ff610ac1c1fe</t>
+          <t>afc1574f-a68f-4fd4-834f-3dfb4ab2585b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08a6bb3e-0cec-4375-b601-984b7dd5fbb7</t>
+          <t>ca359f81-5a15-44b5-ab1e-bdd387bd5abc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4423,10 +7219,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The item passes all checks: the sentence is coherent and appropriate for the SAT, the question is clear and tests the intended skill, the difficulty level is appropriate, the options are valid with one correct answer, and the explanation is accurate and complete.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Correct answer (B) is the only option directly supporting the proponents’ claim about better performance during bad weather (rain). The other options either address clear-day performance (A), provide non-performance rationale (C), or state the council’s citation without additional evidentiary value (D).</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
@@ -4449,7 +7247,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a2e84a25-c7ee-4215-89bd-c6a01194133d</t>
+          <t>7b9ab154-a40c-496f-a110-c06658954890</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4457,12 +7255,10 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>The item successfully tests the ability to correctly handle clause boundaries using punctuation. The sentence is appropriate, the question is clear, and the options provide a suitable challenge for the medium difficulty level. The correct answer is clearly the best choice, and the explanation accurately describes why it is correct.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
@@ -4485,7 +7281,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>e5022311-cf1c-4c24-b42b-a934f609db9f</t>
+          <t>6a4a250b-ad83-47d9-be3b-9135663e30d3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4495,10 +7291,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The item passes all checks: it presents a clear clause-boundary decision, the options are well-formed and challenging, and the correct answer is clearly justified by standard English conventions. The explanation accurately describes why the correct answer is correct and why the others are not.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>The passage provides clear evidence that overall flooding metrics improved (fewer blocks with standing water; shorter duration), while acknowledging persistent flooding near the oldest part. The inference that the system reduced flooding overall but did not eliminate it in every neighborhood is strongly supported. The distractors rely on claims not stated (B: flaw/unusually severe storms; C: gardens outperform pipes; D: system never installed near oldest part). Options are distinct and there is no ambiguity about which inference best fits.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
@@ -4521,7 +7319,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13cc2a32-0d52-4ced-8ed9-fe778301ea8b</t>
+          <t>268ca310-108b-4cc9-8d6a-34cdc4e91186</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4531,10 +7329,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The item passes all checks: the sentence is coherent and appropriate for the SAT, the question is clear and tests the intended skill, the difficulty is aligned with the 'Easy' level, the answer choices are well-formed and distinct, and the explanation correctly justifies the correct answer.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>The question requires inferring the mechanism behind the immediate decline (reduced exposure from cleaner reservoir water) using the passage's timing (reservoir expansion first; sewer lines years later) and causal language. Only option A best fits the supported inference. The other options either assert unsupported timing (B, C) or contradict the passage (D).</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
@@ -4557,7 +7357,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>e1a84ef3-219f-4d16-9cd5-2105e9947016</t>
+          <t>f47875db-c498-4459-b38d-be0f85d7f083</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4567,10 +7367,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The item passes all checks: the sentence is coherent and appropriate for the SAT, the question is clear and tests subject-verb agreement, the difficulty level is appropriate, the answer choices are well-formed with one correct answer, and the explanation accurately describes the reasoning for the correct choice.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>The passage implies an interaction: fog days condition the effect of lighting duration on bird deaths. Option A is the best-supported inference. Options B, C, and D contradict the interaction framing.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
@@ -4593,27 +7395,41 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cd524534-e24f-4f13-b9de-bd7015c565a0</t>
+          <t>b82a52f7-173c-4383-b34b-257819c52eb6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1dc34444-5f0a-4725-b015-a680211f437e</t>
+          <t>d8690b31-5733-47ed-8923-fac7c2e2f521</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4623,10 +7439,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The item passes because it correctly identifies a modifier-placement issue, with option A clearly connecting the modifier to the intended subject. The question is clear, the difficulty is appropriate for an easy level, and the explanation accurately describes why the correct answer is correct and the others are not.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Passage provides concrete week-by-week data for both neighborhoods. Question asks for a best-supported statement about change from Week 1 to Week 6, which requires interpreting the endpoints. Option A is uniquely correct; others are either contradicted by the data or based on incorrect computations.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
@@ -4649,7 +7467,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>69a2971a-a971-4b77-96f3-12512a6925e7</t>
+          <t>71ceb791-8ae7-4f9b-bd56-3d89fa227646</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4657,12 +7475,10 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>The item passes all checks: it clearly tests modifier placement, the question and options are well-formed, and the correct answer is unambiguously correct. The difficulty level is appropriate for the target audience.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
@@ -4685,7 +7501,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5790d328-ff28-4fde-b2f2-fd86f91bcbca</t>
+          <t>713d38a3-0ce6-4e26-941d-49e0998d64f0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4693,11 +7509,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>The item passes because it presents a clear modifier-placement issue, with the correct answer (Option A) resolving the ambiguity by correctly linking the modifier to the intended subject. The question is well-aligned with the 'Modifiers' type and the difficulty level is appropriate, with challenging distractors that require careful consideration. The explanation accurately describes why the correct answer is correct and why the other options are incorrect.</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>1</v>
@@ -4721,7 +7533,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42988be9-a401-4bf8-909e-c77aafca2d51</t>
+          <t>729763cc-00cf-43b6-ae2c-dbe4b81917a6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4731,7 +7543,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The item presents a clear punctuation decision involving two independent clauses. The correct answer uses a semicolon, which is appropriate and aligns with standard English conventions. The explanation accurately describes why the correct answer is correct and why the other options are incorrect. The difficulty level is appropriate for an easy question, and there are no grammatical errors or ambiguities in the item.</t>
+          <t>The item tests punctuation used to mark a nonessential parenthetical ("as expected"), requiring commas before and after. The stem provides sufficient context, the editable portion is correct, and exactly one option (A) is grammatically correct with parallel comma placement.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -4757,7 +7569,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>67575ecf-db02-45b0-a539-be64a8f8b22f</t>
+          <t>86561cc9-8def-4bb2-823e-44b2edac3feb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4767,7 +7579,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The item passes because it presents a clear punctuation decision affecting sentence structure, with one correct answer that follows standard English conventions. The explanation accurately describes why the correct answer is correct and why the others are not. The difficulty level is appropriate, and all options are plausible, with only one being correct.</t>
+          <t>Item has two independent clauses (“the exhibit drew record attendance” and “visitors stayed longer than usual”) that require punctuation before the coordinating conjunction. Option D is the only correct choice; the other options contain run-on punctuation, incorrect semicolon use, or an extra comma after the conjunction.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -4793,7 +7605,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>82e7819c-5dd0-4005-b140-62e8465b37ff</t>
+          <t>d2eaa7af-1e36-445d-8768-b5e1bb755507</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4803,7 +7615,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The item passes all checks: it presents a valid punctuation decision, the question is clear and tests the intended skill, the difficulty level is appropriate, and the explanation correctly justifies the correct answer choice while ruling out the incorrect ones.</t>
+          <t>The blank correctly tests the required verb tense/structure after “but” to match the earlier past tense (“decided”). “postponed announcing” is the only option that forms a correct past-tense verb phrase (“postponed” + gerund “announcing”) and fits the sentence meaning.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -4829,7 +7641,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a114fbd3-5f70-4d71-852b-fe43abd6d532</t>
+          <t>5089b33f-c0e3-481b-9057-d3e7d280f5a3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4837,11 +7649,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>The item effectively tests the ability to choose the appropriate transition word to connect contrasting ideas. The correct answer 'However,' is clearly the best choice to indicate the contrast between historical use and modern scientific validation. The question is clear, the options are well-formed, and the explanation accurately supports the answer choice.</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>1</v>
@@ -4858,80 +7666,54 @@
       <c r="I35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b8bbfecd-675d-4577-8b4c-0c55564f6f51</t>
+          <t>c30ba40f-2b4d-419e-8f49-b120c612b3dd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>The item effectively tests the ability to choose the correct transitional word to express contrast between early beliefs and later observations about stars. The correct answer 'however' is clearly the best choice, and the explanation adequately justifies why the other options are incorrect. The difficulty level is appropriate, and the question is clear and well-constructed.</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>665795ee-29b7-424e-b97d-ca6f92cae8c6</t>
+          <t>d0be5098-41a4-461d-8b84-66bc1d22c1cb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>The item effectively tests the ability to choose the correct transition to connect ideas in a passage. The correct answer, 'subsequently,' accurately reflects the chronological progression from early beliefs to later discoveries. The difficulty is appropriate for a hard-level question, with plausible distractors. The explanation clearly justifies the correct choice and the incorrect options.</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bafc6d2b-3ce8-431f-ab62-ed78f4f0583f</t>
+          <t>379d279a-7d38-4ec8-9fbb-72965c5e2a3b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4939,11 +7721,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>The item passes because it presents a clear and coherent organization question that aligns with the requested difficulty level. The sentence placement decision is straightforward, with one answer choice clearly improving the flow of the passage. The explanation is accurate and supports the correct answer choice effectively.</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>1</v>
@@ -4960,12 +7738,14 @@
       <c r="I38" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08901dcc-f5fd-43b2-adb1-8a8efffeb975</t>
+          <t>8ed754d1-1f41-4b03-b48a-82c0afd913a7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4985,7 +7765,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ccacff95-3604-4334-99a4-489cc90a08c4</t>
+          <t>77b71957-0ca5-4d16-9fcd-9e2e4e4f5104</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4995,7 +7775,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>The item effectively tests the organization of ideas within a short passage. The question is clear and aligns with the 'Organization' question type, requiring the test-taker to determine the most logical sequence of sentences. The difficulty is appropriate for a 'Hard' level, as the decision involves understanding the logical flow of information about photosynthesis. The answer choices are distinct and plausible, with only one correct answer. The explanation accurately justifies the correct answer and addresses the incorrect options.</t>
+          <t>The proposal (singular) requires a singular verb form in the present tense: 'requires.' Only option A matches the required subject-verb agreement for the main clause.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -5014,182 +7794,114 @@
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>92649f81-bef4-4493-a2dd-a3ee5042f2ed</t>
+          <t>be4f7432-001d-4c96-bc8c-05afab1b9858</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>The item passes all checks as it presents a clear and concise question about concision and precision. The correct answer is clearly the most concise option, and the explanation appropriately justifies this choice. The difficulty level is aligned with the 'Easy' target, and all answer choices are plausible, with only one being correct.</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>e10c9545-0155-498d-9a21-06722be9690c</t>
+          <t>becad836-46a3-4d00-834b-be9362612f3d</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>The item effectively tests concision and precision by asking for the clearest and most concise revision of the sentence. The correct answer is clearly the most concise and precise, and the explanation accurately supports this choice. The difficulty level is appropriate, and the distractors are plausible yet clearly less effective than the correct answer.</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1</v>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>931a44f5-6b96-47c5-a727-8ffdbc1d2df8</t>
+          <t>745cd9ab-c731-40b1-b83d-98a070cbcef3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>The item effectively tests concision and precision by asking for the clearest and most concise expression of a metaphorical concept. The correct answer is clearly the most concise and precise, and the explanation accurately justifies this choice. The difficulty level is appropriate, with distractors that are plausible but less effective than the correct answer.</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>b3ba1550-1b5e-471f-8a0c-64e3d6233317</t>
+          <t>339dad6f-2ab8-46c1-9a56-3bb554ed7d83</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>The item effectively tests the ability to identify the main finding of a study, aligning with the Rhetorical Synthesis question type. The question is clear, the difficulty is appropriate for an easy-level question, and the explanation correctly identifies why option A is the best choice. The item is well-constructed with no ambiguity or errors.</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>eab28c65-a9ee-4128-abf0-05e34395306e</t>
+          <t>0a803dd9-182d-4ad2-8e89-9f8e9c720906</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>The item successfully meets all the criteria for a Rhetorical Synthesis question. The sentence provides sufficient context for evaluating the spread of cultural practices, and the question is clear and appropriately challenging. The correct answer is clearly justified, and the explanation effectively distinguishes between the options.</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6668f499-cee4-4f3a-bed0-b8764079cab2</t>
+          <t>562b18a7-bdb3-4b23-bdff-7022e3fc65a5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5199,7 +7911,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>The item effectively tests the ability to identify the choice that best emphasizes uncertainty about the interactions between the coastal settlement and neighboring regions. The question is clear and precise, the options are well-formed and appropriately challenging, and the explanation correctly justifies the correct answer. The difficulty level is aligned with the 'Hard' target, as the distinctions between the options require careful consideration of the nuances in meaning.</t>
+          <t>The sentence presents a clear punctuation decision involving a semicolon joining two independent clauses and the comma required after however when used to introduce the second clause. Option A is uniquely correct; B and C omit required comma/semicolon separation for the clauses, and D adds an unnecessary final comma.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -5218,7 +7930,1295 @@
       <c r="I46" t="n">
         <v>1</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>843a1e08-ecd4-4ae7-90e0-6d6c2447e82a</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>d97b5f05-37fe-4394-867f-2b0e777b7d38</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cause-and-effect relationship between reducing wait times and increased attendance; exactly one option fits that logic (“as a result”). Options are parallel transition phrases and clearly distract by offering contrast, example, or addition.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>21888742-213b-4762-a728-e86ef2acea96</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The blank requires a transition marking contrast between improved predictive accuracy and the limitation that errors remain concentrated, alongside the authors’ decision not to fully claim reliability. “However” uniquely provides this contrast; the other options misrepresent the relationship (causal conclusion, supplementation, or illustration). All options are distinct and parallel transition words.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ba7adbe5-38d3-4db9-81ba-0b4a4bad367a</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7653e63e-317a-4536-a073-a7eaada710ef</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6e87a69c-c010-4cfd-90f5-faa4d8e83d49</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2a474f69-206a-4666-b816-45fb167e1325</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>f241fd30-3a4b-42bb-bd34-cdd24c75c95f</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>The original sentence includes unnecessary phrasing (“they believe,” “that it be,” “recommend that it be revised”). Option A removes those redundancies while preserving meaning. The distractors reflect plausible concision/punctuation choices but introduce either unnecessary wording, an altered logic cue, or insufficient concision. The task is clearly about concision and precision rather than grammar alone.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0962360f-7c42-4f08-9297-4aecf41ef1dc</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2de9072e-4d7e-429d-a039-ec702891724f</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The item asks for the best synthesis of the sentence’s stated reasoning (measuring first provides baseline data for achievable waste-reduction targets). Option A matches directly; B, C, and D propose different rationales unrelated to establishing targets via baseline data. Options are parallel and mutually exclusive.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>9ea24e10-26aa-413d-af75-0394c87eba55</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1194b008-b613-40ea-bcee-dbeb351b238d</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Clarity issue: The prompt asks to preserve the contrast-and-conclusion relationship by keeping the stated reason, but the item is presented as a full sentence with the editable portion already including 'however' and the reason. Despite this, the question remains answerable and the correct option is unambiguous.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>744da5f7-601f-4f54-99b2-2bd82b12922f</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>f2c15c0f-6c6e-4162-b558-a61991adb238</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1515fa0a-b42c-4665-bfb7-af1c13b238bc</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>84fdeb9b-6547-43f5-be38-aa72632683f2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>05e14355-29e0-4b52-ac91-91cf317f1d93</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>7ba77145-1c7a-443c-b005-f3449df4471b</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>The decision tests correct subject-verb agreement in a relative clause: 'the departments that [HAVE] not yet submitted their estimates.' The other options introduce incorrect tense/person or an incorrect auxiliary sequence ('has', 'has had', 'have had'). The explanation correctly identifies the plural subject 'departments' and supports 'have.'</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>98512507-732d-4866-9f5d-0cf18a129bf3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1b5d9c1c-9503-483b-a408-adaf5cc53e91</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>869f5a65-5014-47b3-86b2-1dd2bccaa761</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>aa0413f0-ac81-4af7-9980-5539e984dbc1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>809ba6bc-4281-40e7-b14c-8a0d6b21ace5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>The passage provides clear context: “improvement” language masks a different goal (“reducing theft”). Therefore, “concealed” aligns with “hidden.” The other options are either opposites or irrelevant.</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6dc23140-a112-4423-8aa1-c06fa94535ad</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>The passage provides a clear contrast: the term “buffer” is said to obscure a conditional mechanism. The correct option, “hides or masks,” matches the rhetorical use and the explanation accurately ties the meaning to the conditional nature described.</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>731d733d-7d10-43f1-8321-4c0931ea979c</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>The passage has a clear structure: general claim → examples → clarification/limitation → explanation of mechanisms → solution. Option A best matches this progression. The other options conflict with the passage’s stated claims (e.g., automatic improvement, unnecessary reading, listing reasons students struggle).</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>058e7f83-e79d-403b-9591-893f4ae559bd</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1007e84f-18d0-4d07-86c1-d43f19728571</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>The passage moves from an earlier interpretation to a revised one, then explains how that revision changes the events’ meaning and concludes with a functional summary. Option A matches the passage’s overall organizational structure. Other options describe different structures (list/conclude, chronology, competing explanations) that are not supported by the text.</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>299d128b-6ecd-47b8-9bcb-d5c3c94c168f</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Text 1 raises an ecological concern (stray streetlight disrupts insects). Text 2 responds directly by proposing glare reduction/directional lighting (downward shields) and timing changes to limit stray glow while maintaining road visibility. Option B is the only choice that accurately reflects that response.</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7cc40593-8be7-4734-a93a-de6b19a89657</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Text 1 and Text 2 both address reconstructive memory; Text 2 narrows the mechanism by adding that institutional/legal language constrains reconstruction. Option A uniquely matches this relationship. The other options introduce claims not present in the texts (direct replay, emotional reactions only, or reconstruction only via comparing witnesses).</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>87479ff1-f97a-4800-b99b-014e5da82a15</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>All information needed to answer is present in the two texts. Text 2 directly modifies Text 1 by specifying how rhetoric of causation can mislead (compression of competing motives into a moral narrative and reflection of author intent). Only option A captures both the mechanism and the reframing relative to Text 1; the other options introduce claims not supported by the passages or are overly absolute.</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ae1143c0-c4a3-4ffd-bc13-b3eacd0c7b48</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Central idea is that protecting drinking water and reducing outbreaks required multiple coordinated actions affecting both water supply and waste removal. Option A best captures this synthesis. Other options either overemphasize one component (B, C), introduce incorrect cause (B), or contradict the “more than one action” conclusion (B, D) and the passage’s discussion of waste separation and drainage (C, D).</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>92320f13-067b-4a3a-98a6-235415469c25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Passage presents a single central idea: standardizing measurements and timing improved cross-city outbreak comparison and also changed observed patterns. Option A best synthesizes both aspects. Options B, C, and D introduce unsupported or contradicted claims.</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>74666fdd-00a4-4b1a-bc40-221f5db6c15d</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3b9bb8cd-bb1f-4f9e-b01d-bf05a184f720</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Passage clearly states the council’s conclusion: strongest reasons were brightness and controllability. Option A directly supports those reasons. Other options address counterpoints (repairs concern) or a different claim (crime). Question is specific and answerable from the passage.</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2ff565ff-2aa6-4fdc-bc38-d5f6589d3878</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>The question asks which part most strongly supports the causal claim by showing theft decreased after implementation. Option C directly provides the post-installation theft reduction figure, while A is only an estimate and B/D do not demonstrate decreased theft after implementation.</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0e9ebb11-a639-4faf-a45f-1bf52f569570</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Passage clearly sets up a claim about measurement preceding improvements and provides three cities’ evidence sequences. The question asks for the piece of evidence most directly supporting the claim, which tests evidence selection (Command of Evidence). Option A is the only one that shows a clean measurement-then-improvement sequence across the timeline; B includes confounds (irregular changes pre-1930) and C attributes improvement mainly to another event. Option D is not evidence but a restatement of dependence, so it is clearly incorrect. Explanation correctly justifies why A is strongest and why others are less direct.</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>d343c9e6-a135-493b-be5f-5eb63e8c75ee</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>a78ade76-ff44-48cb-8016-c91a822fb0a6</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>The passage provides evidence of larger chlorine swings and bacterial spikes in Neighborhood B compared with Neighborhood A, and concludes timing of dosage changes affects bacterial growth. Option A is the strongest inference consistent with the described dosage schedules and the observed spikes. Options B and C rely on unstated causes; option D is an overreach.</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>23cf3f3f-f602-40cc-aabc-45f2e3b7b41d</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PASS. The inference requires connecting (i) oxygen decline at 10 meters and (ii) decreased fish presence at 10 meters over the same afternoon period, including the added control that rules out light/temperature as the primary driver. Option A is the best-supported inference. Options B, C, and D introduce causes/conditions not supported by the passage.</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>89be43d1-35db-4eb4-87d5-e5741543f764</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86e8a76a-07c9-4ca1-9fba-370f951207c6</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Question directly uses the provided eight-week averages (17% and 13%), requires a simple subtraction to interpret the data, and has exactly one correct option. Explanation matches the arithmetic.</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>d42e3c6e-756c-45a0-ad90-06366374edae</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Passage provides all needed numerical data (percentages and constant total). Question requires interpreting the data and converting percentages to counts, then computing a difference. Options are distinct and plausible, with exactly one correct. Explanation correctly calculates 24,000 fewer commuters.</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
